--- a/factor_output.xlsx
+++ b/factor_output.xlsx
@@ -47167,7 +47167,7 @@
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-07</t>
+          <t>Generated: 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -48465,7 +48465,7 @@
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-07</t>
+          <t>Generated: 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -49838,7 +49838,7 @@
       </c>
       <c r="B54" s="27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/factor_output.xlsx
+++ b/factor_output.xlsx
@@ -1528,90 +1528,90 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>CF Industries Holdings, Inc.</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>93</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>40</v>
+        <v>74.09999999999999</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>32.5</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>36.8</v>
+        <v>77.40000000000001</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>88.7</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v>16</v>
+        <v>80.59999999999999</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>71</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>68.40000000000001</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>98.61</v>
+        <v>98.8</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>68.2</v>
+        <v>71</v>
       </c>
       <c r="O8" s="9" t="n">
         <v>7</v>
       </c>
       <c r="P8" s="10" t="n">
-        <v>20.46</v>
+        <v>19.56</v>
       </c>
       <c r="Q8" s="10" t="n">
-        <v>18.52</v>
+        <v>16.3</v>
       </c>
       <c r="R8" s="10" t="n">
-        <v>5.21</v>
+        <v>4.22</v>
       </c>
       <c r="S8" s="10" t="n">
-        <v>10.35</v>
+        <v>10.06</v>
       </c>
       <c r="T8" s="10" t="n">
-        <v>5.37</v>
+        <v>1.8</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>3.68</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>0.8</v>
+        <v>3.55</v>
       </c>
       <c r="X8" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="9" t="b">
         <v>0</v>
@@ -1624,90 +1624,90 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>CF Industries Holdings, Inc.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>88.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>32.5</v>
+        <v>84.2</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>40</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="H9" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>88.7</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>36.8</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>71</v>
+        <v>80</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>16</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>68.40000000000001</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>98.8</v>
+        <v>98.61</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>71</v>
+        <v>68.2</v>
       </c>
       <c r="O9" s="9" t="n">
         <v>7</v>
       </c>
       <c r="P9" s="10" t="n">
-        <v>19.56</v>
+        <v>20.46</v>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>16.3</v>
+        <v>18.52</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>4.22</v>
+        <v>5.21</v>
       </c>
       <c r="S9" s="10" t="n">
-        <v>10.06</v>
+        <v>10.35</v>
       </c>
       <c r="T9" s="10" t="n">
-        <v>1.8</v>
+        <v>5.37</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>8.869999999999999</v>
+        <v>3.68</v>
       </c>
       <c r="V9" s="10" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="W9" s="10" t="n">
-        <v>3.55</v>
+        <v>0.8</v>
       </c>
       <c r="X9" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z9" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB9" s="9" t="b">
         <v>0</v>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>88.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>66.7</v>
@@ -2826,7 +2826,7 @@
         <v>20</v>
       </c>
       <c r="P21" s="10" t="n">
-        <v>19.46</v>
+        <v>19.55</v>
       </c>
       <c r="Q21" s="10" t="n">
         <v>14.66</v>
@@ -2988,7 +2988,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>57.7</v>
+        <v>56.6</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>61.5</v>
@@ -3006,13 +3006,13 @@
         <v>8.5</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M23" s="9" t="n">
         <v>95.81999999999999</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>73.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="O23" s="9" t="n">
         <v>22</v>
@@ -3024,7 +3024,7 @@
         <v>14.88</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>7.5</v>
+        <v>7.36</v>
       </c>
       <c r="S23" s="10" t="n">
         <v>7.99</v>
@@ -5195,7 +5195,7 @@
       <c r="E46" s="6" t="n">
         <v>65.8</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="7" t="n">
         <v>35.9</v>
       </c>
       <c r="G46" s="6" t="n">
@@ -6424,93 +6424,93 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>LVS</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas Sands Corp.</t>
+          <t>Quest Diagnostics Incorporated</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="E59" s="7" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="G59" s="11" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="H59" s="7" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="I59" s="8" t="n">
-        <v>56</v>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="I59" s="7" t="n">
+        <v>51.1</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="K59" s="6" t="n">
-        <v>93.59999999999999</v>
+        <v>72.90000000000001</v>
+      </c>
+      <c r="K59" s="7" t="n">
+        <v>37.3</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>60.7</v>
+        <v>60.6</v>
       </c>
       <c r="M59" s="9" t="n">
         <v>88.65000000000001</v>
       </c>
       <c r="N59" s="9" t="n">
-        <v>74.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O59" s="9" t="n">
         <v>58</v>
       </c>
       <c r="P59" s="10" t="n">
-        <v>17.45</v>
+        <v>13.96</v>
       </c>
       <c r="Q59" s="10" t="n">
-        <v>9.779999999999999</v>
+        <v>11.55</v>
       </c>
       <c r="R59" s="10" t="n">
-        <v>11.65</v>
+        <v>5.95</v>
       </c>
       <c r="S59" s="10" t="n">
-        <v>3.75</v>
+        <v>9.06</v>
       </c>
       <c r="T59" s="10" t="n">
-        <v>4.86</v>
+        <v>9.49</v>
       </c>
       <c r="U59" s="10" t="n">
-        <v>5.6</v>
+        <v>5.11</v>
       </c>
       <c r="V59" s="10" t="n">
-        <v>2.93</v>
+        <v>3.64</v>
       </c>
       <c r="W59" s="10" t="n">
-        <v>4.68</v>
+        <v>1.86</v>
       </c>
       <c r="X59" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y59" s="9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="Z59" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA59" s="9" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="AB59" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC59" s="9" t="n"/>
       <c r="AD59" s="9" t="b">
@@ -6520,42 +6520,42 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Quest Diagnostics Incorporated</t>
+          <t>Las Vegas Sands Corp.</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="G60" s="8" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="H60" s="6" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="I60" s="7" t="n">
-        <v>51.1</v>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="G60" s="11" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="I60" s="8" t="n">
+        <v>56</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="K60" s="7" t="n">
-        <v>37.3</v>
+        <v>58.7</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>93.59999999999999</v>
       </c>
       <c r="L60" s="6" t="n">
         <v>60.6</v>
@@ -6564,49 +6564,49 @@
         <v>88.45</v>
       </c>
       <c r="N60" s="9" t="n">
-        <v>78.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O60" s="9" t="n">
         <v>59</v>
       </c>
       <c r="P60" s="10" t="n">
-        <v>13.96</v>
+        <v>17.36</v>
       </c>
       <c r="Q60" s="10" t="n">
-        <v>11.55</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="R60" s="10" t="n">
-        <v>5.95</v>
+        <v>11.65</v>
       </c>
       <c r="S60" s="10" t="n">
-        <v>9.06</v>
+        <v>3.75</v>
       </c>
       <c r="T60" s="10" t="n">
-        <v>9.49</v>
+        <v>4.86</v>
       </c>
       <c r="U60" s="10" t="n">
-        <v>5.11</v>
+        <v>5.6</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>3.64</v>
+        <v>2.93</v>
       </c>
       <c r="W60" s="10" t="n">
-        <v>1.86</v>
+        <v>4.68</v>
       </c>
       <c r="X60" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y60" s="9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Z60" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA60" s="9" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="AB60" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC60" s="9" t="n"/>
       <c r="AD60" s="9" t="b">
@@ -9976,90 +9976,90 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Regency Centers Corporation</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="E96" s="7" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="F96" s="7" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="G96" s="7" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="H96" s="6" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="I96" s="8" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="J96" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="K96" s="7" t="n">
-        <v>40</v>
+        <v>57.8</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="G96" s="11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H96" s="8" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="J96" s="8" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="K96" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="L96" s="6" t="n">
         <v>57.4</v>
       </c>
       <c r="M96" s="9" t="n">
-        <v>81.27</v>
+        <v>81.08</v>
       </c>
       <c r="N96" s="9" t="n">
-        <v>73.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="O96" s="9" t="n">
         <v>95</v>
       </c>
       <c r="P96" s="10" t="n">
-        <v>13.86</v>
+        <v>12.72</v>
       </c>
       <c r="Q96" s="10" t="n">
-        <v>10.8</v>
+        <v>14.03</v>
       </c>
       <c r="R96" s="10" t="n">
-        <v>5.87</v>
+        <v>9.31</v>
       </c>
       <c r="S96" s="10" t="n">
-        <v>5.83</v>
+        <v>3.04</v>
       </c>
       <c r="T96" s="10" t="n">
-        <v>9.19</v>
+        <v>5.21</v>
       </c>
       <c r="U96" s="10" t="n">
-        <v>5.82</v>
+        <v>7.76</v>
       </c>
       <c r="V96" s="10" t="n">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="W96" s="10" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="X96" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y96" s="9" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="Z96" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA96" s="9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB96" s="9" t="b">
         <v>0</v>
@@ -10072,90 +10072,90 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Regency Centers Corporation</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="E97" s="8" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="F97" s="6" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="G97" s="11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="H97" s="8" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="I97" s="6" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="J97" s="8" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="K97" s="8" t="n">
-        <v>50</v>
+        <v>63</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="F97" s="7" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="G97" s="7" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="I97" s="8" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="K97" s="7" t="n">
+        <v>40</v>
       </c>
       <c r="L97" s="6" t="n">
         <v>57.4</v>
       </c>
       <c r="M97" s="9" t="n">
-        <v>81.08</v>
+        <v>81.27</v>
       </c>
       <c r="N97" s="9" t="n">
-        <v>78.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="O97" s="9" t="n">
         <v>95</v>
       </c>
       <c r="P97" s="10" t="n">
-        <v>12.72</v>
+        <v>13.86</v>
       </c>
       <c r="Q97" s="10" t="n">
-        <v>14.03</v>
+        <v>10.8</v>
       </c>
       <c r="R97" s="10" t="n">
-        <v>9.31</v>
+        <v>5.87</v>
       </c>
       <c r="S97" s="10" t="n">
-        <v>3.04</v>
+        <v>5.83</v>
       </c>
       <c r="T97" s="10" t="n">
-        <v>5.21</v>
+        <v>9.19</v>
       </c>
       <c r="U97" s="10" t="n">
-        <v>7.76</v>
+        <v>5.82</v>
       </c>
       <c r="V97" s="10" t="n">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="W97" s="10" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="X97" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y97" s="9" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="Z97" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA97" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB97" s="9" t="b">
         <v>0</v>
@@ -10264,93 +10264,93 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Broadridge Financial Solutions,</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="E99" s="6" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="F99" s="6" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="G99" s="7" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="H99" s="6" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="I99" s="8" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="J99" s="11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K99" s="11" t="n">
-        <v>0</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F99" s="7" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="G99" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H99" s="7" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="I99" s="6" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="J99" s="8" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="K99" s="8" t="n">
+        <v>51.9</v>
       </c>
       <c r="L99" s="6" t="n">
         <v>57.3</v>
       </c>
       <c r="M99" s="9" t="n">
-        <v>80.48</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="N99" s="9" t="n">
-        <v>60.4</v>
+        <v>73</v>
       </c>
       <c r="O99" s="9" t="n">
         <v>98</v>
       </c>
       <c r="P99" s="10" t="n">
-        <v>9.18</v>
+        <v>18.31</v>
       </c>
       <c r="Q99" s="10" t="n">
-        <v>16.32</v>
+        <v>13.6</v>
       </c>
       <c r="R99" s="10" t="n">
-        <v>12.58</v>
+        <v>6.05</v>
       </c>
       <c r="S99" s="10" t="n">
-        <v>6.42</v>
+        <v>1.43</v>
       </c>
       <c r="T99" s="10" t="n">
-        <v>7.26</v>
+        <v>5.04</v>
       </c>
       <c r="U99" s="10" t="n">
-        <v>5.43</v>
+        <v>6.46</v>
       </c>
       <c r="V99" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.78</v>
       </c>
       <c r="W99" s="10" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X99" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y99" s="9" t="n">
-        <v>0</v>
+        <v>22.6</v>
       </c>
       <c r="Z99" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA99" s="9" t="n">
-        <v>30.5</v>
+        <v>0</v>
       </c>
       <c r="AB99" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC99" s="9" t="n"/>
       <c r="AD99" s="9" t="b">
@@ -10360,93 +10360,93 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions,</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="E100" s="8" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F100" s="7" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="G100" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="H100" s="7" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="I100" s="6" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="J100" s="8" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="K100" s="8" t="n">
-        <v>51.9</v>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="H100" s="6" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="I100" s="8" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="J100" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K100" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="L100" s="6" t="n">
         <v>57.3</v>
       </c>
       <c r="M100" s="9" t="n">
-        <v>80.68000000000001</v>
+        <v>80.48</v>
       </c>
       <c r="N100" s="9" t="n">
-        <v>73</v>
+        <v>60.4</v>
       </c>
       <c r="O100" s="9" t="n">
         <v>98</v>
       </c>
       <c r="P100" s="10" t="n">
-        <v>18.31</v>
+        <v>9.18</v>
       </c>
       <c r="Q100" s="10" t="n">
-        <v>13.6</v>
+        <v>16.32</v>
       </c>
       <c r="R100" s="10" t="n">
-        <v>6.05</v>
+        <v>12.58</v>
       </c>
       <c r="S100" s="10" t="n">
-        <v>1.43</v>
+        <v>6.42</v>
       </c>
       <c r="T100" s="10" t="n">
-        <v>5.04</v>
+        <v>7.26</v>
       </c>
       <c r="U100" s="10" t="n">
-        <v>6.46</v>
+        <v>5.43</v>
       </c>
       <c r="V100" s="10" t="n">
-        <v>3.78</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W100" s="10" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X100" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y100" s="9" t="n">
-        <v>22.6</v>
+        <v>0</v>
       </c>
       <c r="Z100" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA100" s="9" t="n">
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="AB100" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC100" s="9" t="n"/>
       <c r="AD100" s="9" t="b">
@@ -17560,12 +17560,12 @@
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Rockwell Automation, Inc.</t>
+          <t>Veralto Corp</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
@@ -17573,71 +17573,71 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D175" s="11" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="E175" s="6" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="F175" s="8" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="G175" s="8" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="H175" s="7" t="n">
-        <v>45.3</v>
+      <c r="D175" s="8" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="F175" s="7" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="G175" s="11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="H175" s="6" t="n">
+        <v>73.90000000000001</v>
       </c>
       <c r="I175" s="8" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="J175" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="K175" s="6" t="n">
-        <v>84</v>
+        <v>59.2</v>
+      </c>
+      <c r="J175" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="K175" s="11" t="n">
+        <v>12.3</v>
       </c>
       <c r="L175" s="8" t="n">
         <v>53.4</v>
       </c>
       <c r="M175" s="9" t="n">
-        <v>65.34</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="N175" s="9" t="n">
-        <v>73.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O175" s="9" t="n">
         <v>174</v>
       </c>
       <c r="P175" s="10" t="n">
-        <v>4.57</v>
+        <v>12.5</v>
       </c>
       <c r="Q175" s="10" t="n">
-        <v>15.82</v>
+        <v>13.64</v>
       </c>
       <c r="R175" s="10" t="n">
-        <v>7.23</v>
+        <v>6.05</v>
       </c>
       <c r="S175" s="10" t="n">
-        <v>9.26</v>
+        <v>3.67</v>
       </c>
       <c r="T175" s="10" t="n">
-        <v>4.53</v>
+        <v>7.39</v>
       </c>
       <c r="U175" s="10" t="n">
-        <v>5.26</v>
+        <v>5.92</v>
       </c>
       <c r="V175" s="10" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="W175" s="10" t="n">
-        <v>4.2</v>
+        <v>0.62</v>
       </c>
       <c r="X175" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y175" s="9" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Z175" s="9" t="b">
         <v>0</v>
@@ -17656,12 +17656,12 @@
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>ROK</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>Veralto Corp</t>
+          <t>Rockwell Automation, Inc.</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
@@ -17669,71 +17669,71 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D176" s="8" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="E176" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="F176" s="7" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="G176" s="11" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="H176" s="6" t="n">
-        <v>73.90000000000001</v>
+      <c r="D176" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E176" s="6" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="F176" s="8" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="G176" s="8" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="H176" s="7" t="n">
+        <v>45.3</v>
       </c>
       <c r="I176" s="8" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="J176" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="K176" s="11" t="n">
-        <v>12.3</v>
+        <v>52.6</v>
+      </c>
+      <c r="J176" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K176" s="6" t="n">
+        <v>84</v>
       </c>
       <c r="L176" s="8" t="n">
         <v>53.4</v>
       </c>
       <c r="M176" s="9" t="n">
-        <v>65.54000000000001</v>
+        <v>65.34</v>
       </c>
       <c r="N176" s="9" t="n">
-        <v>71.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="O176" s="9" t="n">
         <v>174</v>
       </c>
       <c r="P176" s="10" t="n">
-        <v>12.5</v>
+        <v>4.57</v>
       </c>
       <c r="Q176" s="10" t="n">
-        <v>13.64</v>
+        <v>15.82</v>
       </c>
       <c r="R176" s="10" t="n">
-        <v>6.05</v>
+        <v>7.23</v>
       </c>
       <c r="S176" s="10" t="n">
-        <v>3.67</v>
+        <v>9.26</v>
       </c>
       <c r="T176" s="10" t="n">
-        <v>7.39</v>
+        <v>4.53</v>
       </c>
       <c r="U176" s="10" t="n">
-        <v>5.92</v>
+        <v>5.26</v>
       </c>
       <c r="V176" s="10" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="W176" s="10" t="n">
-        <v>0.62</v>
+        <v>4.2</v>
       </c>
       <c r="X176" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y176" s="9" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Z176" s="9" t="b">
         <v>0</v>
@@ -17848,90 +17848,90 @@
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cognizant Technology Solutions </t>
+          <t>West Pharmaceutical Services, I</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="E178" s="7" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F178" s="11" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G178" s="11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H178" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="I178" s="11" t="n">
-        <v>16.3</v>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="D178" s="11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E178" s="6" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="F178" s="7" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="G178" s="6" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="H178" s="7" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="I178" s="8" t="n">
+        <v>60.7</v>
       </c>
       <c r="J178" s="6" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="K178" s="6" t="n">
-        <v>76.7</v>
+        <v>76.3</v>
+      </c>
+      <c r="K178" s="8" t="n">
+        <v>59.3</v>
       </c>
       <c r="L178" s="8" t="n">
         <v>53.2</v>
       </c>
       <c r="M178" s="9" t="n">
-        <v>64.94</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="N178" s="9" t="n">
-        <v>65.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="O178" s="9" t="n">
         <v>177</v>
       </c>
       <c r="P178" s="10" t="n">
-        <v>20.84</v>
+        <v>3.34</v>
       </c>
       <c r="Q178" s="10" t="n">
-        <v>10.32</v>
+        <v>16.27</v>
       </c>
       <c r="R178" s="10" t="n">
-        <v>3.34</v>
+        <v>5.99</v>
       </c>
       <c r="S178" s="10" t="n">
-        <v>2.93</v>
+        <v>10.51</v>
       </c>
       <c r="T178" s="10" t="n">
-        <v>6.4</v>
+        <v>4.24</v>
       </c>
       <c r="U178" s="10" t="n">
-        <v>1.63</v>
+        <v>6.07</v>
       </c>
       <c r="V178" s="10" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="W178" s="10" t="n">
-        <v>3.84</v>
+        <v>2.97</v>
       </c>
       <c r="X178" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y178" s="9" t="n">
-        <v>31.6</v>
+        <v>0</v>
       </c>
       <c r="Z178" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA178" s="9" t="n">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="AB178" s="9" t="b">
         <v>0</v>
@@ -17944,90 +17944,90 @@
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services, I</t>
+          <t xml:space="preserve">Cognizant Technology Solutions </t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="D179" s="11" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="E179" s="6" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="F179" s="7" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="G179" s="6" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="H179" s="7" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="I179" s="8" t="n">
-        <v>60.7</v>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="E179" s="7" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G179" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H179" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="I179" s="11" t="n">
+        <v>16.3</v>
       </c>
       <c r="J179" s="6" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="K179" s="8" t="n">
-        <v>59.3</v>
+        <v>78.09999999999999</v>
+      </c>
+      <c r="K179" s="6" t="n">
+        <v>76.7</v>
       </c>
       <c r="L179" s="8" t="n">
         <v>53.2</v>
       </c>
       <c r="M179" s="9" t="n">
-        <v>64.73999999999999</v>
+        <v>64.94</v>
       </c>
       <c r="N179" s="9" t="n">
-        <v>73.59999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="O179" s="9" t="n">
         <v>177</v>
       </c>
       <c r="P179" s="10" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="Q179" s="10" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="R179" s="10" t="n">
         <v>3.34</v>
       </c>
-      <c r="Q179" s="10" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="R179" s="10" t="n">
-        <v>5.99</v>
-      </c>
       <c r="S179" s="10" t="n">
-        <v>10.51</v>
+        <v>2.93</v>
       </c>
       <c r="T179" s="10" t="n">
-        <v>4.24</v>
+        <v>6.4</v>
       </c>
       <c r="U179" s="10" t="n">
-        <v>6.07</v>
+        <v>1.63</v>
       </c>
       <c r="V179" s="10" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="W179" s="10" t="n">
-        <v>2.97</v>
+        <v>3.84</v>
       </c>
       <c r="X179" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y179" s="9" t="n">
-        <v>0</v>
+        <v>31.6</v>
       </c>
       <c r="Z179" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA179" s="9" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="AB179" s="9" t="b">
         <v>0</v>
@@ -18040,90 +18040,90 @@
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D180" s="7" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="E180" s="8" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="F180" s="8" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="G180" s="8" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="H180" s="6" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="I180" s="8" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="J180" s="11" t="n">
-        <v>4.8</v>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="E180" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G180" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H180" s="8" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="I180" s="11" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J180" s="7" t="n">
+        <v>42.5</v>
       </c>
       <c r="K180" s="8" t="n">
-        <v>61.9</v>
+        <v>57.5</v>
       </c>
       <c r="L180" s="8" t="n">
         <v>53.1</v>
       </c>
       <c r="M180" s="9" t="n">
-        <v>64.34</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="N180" s="9" t="n">
-        <v>72.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="O180" s="9" t="n">
         <v>179</v>
       </c>
       <c r="P180" s="10" t="n">
-        <v>9.43</v>
+        <v>20.99</v>
       </c>
       <c r="Q180" s="10" t="n">
-        <v>11.79</v>
+        <v>14.3</v>
       </c>
       <c r="R180" s="10" t="n">
-        <v>7.96</v>
+        <v>2.84</v>
       </c>
       <c r="S180" s="10" t="n">
-        <v>7.95</v>
+        <v>1.35</v>
       </c>
       <c r="T180" s="10" t="n">
-        <v>7.41</v>
+        <v>5.69</v>
       </c>
       <c r="U180" s="10" t="n">
-        <v>5.25</v>
+        <v>2.96</v>
       </c>
       <c r="V180" s="10" t="n">
-        <v>0.24</v>
+        <v>2.12</v>
       </c>
       <c r="W180" s="10" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="X180" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y180" s="9" t="n">
-        <v>0</v>
+        <v>32.9</v>
       </c>
       <c r="Z180" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA180" s="9" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="AB180" s="9" t="b">
         <v>0</v>
@@ -18136,90 +18136,90 @@
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>ExxonMobil Holdings Corporation</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D181" s="6" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="E181" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="F181" s="11" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="G181" s="11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="H181" s="8" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="I181" s="11" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="J181" s="7" t="n">
-        <v>42.5</v>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E181" s="8" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F181" s="8" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="G181" s="8" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="H181" s="6" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="I181" s="8" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="J181" s="11" t="n">
+        <v>4.8</v>
       </c>
       <c r="K181" s="8" t="n">
-        <v>57.5</v>
+        <v>61.9</v>
       </c>
       <c r="L181" s="8" t="n">
         <v>53.1</v>
       </c>
       <c r="M181" s="9" t="n">
-        <v>64.54000000000001</v>
+        <v>64.34</v>
       </c>
       <c r="N181" s="9" t="n">
-        <v>65.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="O181" s="9" t="n">
         <v>179</v>
       </c>
       <c r="P181" s="10" t="n">
-        <v>20.99</v>
+        <v>9.43</v>
       </c>
       <c r="Q181" s="10" t="n">
-        <v>14.3</v>
+        <v>11.79</v>
       </c>
       <c r="R181" s="10" t="n">
-        <v>2.84</v>
+        <v>7.96</v>
       </c>
       <c r="S181" s="10" t="n">
-        <v>1.35</v>
+        <v>7.95</v>
       </c>
       <c r="T181" s="10" t="n">
-        <v>5.69</v>
+        <v>7.41</v>
       </c>
       <c r="U181" s="10" t="n">
-        <v>2.96</v>
+        <v>5.25</v>
       </c>
       <c r="V181" s="10" t="n">
-        <v>2.12</v>
+        <v>0.24</v>
       </c>
       <c r="W181" s="10" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="X181" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y181" s="9" t="n">
-        <v>32.9</v>
+        <v>0</v>
       </c>
       <c r="Z181" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA181" s="9" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="AB181" s="9" t="b">
         <v>0</v>
@@ -18712,90 +18712,90 @@
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>Garmin Ltd.</t>
+          <t>Essex Property Trust, Inc.</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D187" s="11" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E187" s="8" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="F187" s="8" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="G187" s="6" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="H187" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="I187" s="6" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="J187" s="7" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="K187" s="7" t="n">
-        <v>27.7</v>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D187" s="8" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="E187" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="F187" s="7" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="G187" s="8" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="H187" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="I187" s="11" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="J187" s="8" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="K187" s="6" t="n">
+        <v>83.3</v>
       </c>
       <c r="L187" s="8" t="n">
         <v>53</v>
       </c>
       <c r="M187" s="9" t="n">
-        <v>63.15</v>
+        <v>62.95</v>
       </c>
       <c r="N187" s="9" t="n">
-        <v>72.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="O187" s="9" t="n">
         <v>186</v>
       </c>
       <c r="P187" s="10" t="n">
-        <v>6.45</v>
+        <v>12</v>
       </c>
       <c r="Q187" s="10" t="n">
-        <v>12.58</v>
+        <v>10.57</v>
       </c>
       <c r="R187" s="10" t="n">
-        <v>7.39</v>
+        <v>6.27</v>
       </c>
       <c r="S187" s="10" t="n">
-        <v>11.4</v>
+        <v>8.52</v>
       </c>
       <c r="T187" s="10" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="U187" s="10" t="n">
-        <v>6.41</v>
+        <v>1.63</v>
       </c>
       <c r="V187" s="10" t="n">
-        <v>2.17</v>
+        <v>2.83</v>
       </c>
       <c r="W187" s="10" t="n">
-        <v>1.38</v>
+        <v>4.17</v>
       </c>
       <c r="X187" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y187" s="9" t="n">
-        <v>0</v>
+        <v>20.4</v>
       </c>
       <c r="Z187" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA187" s="9" t="n">
-        <v>0</v>
+        <v>21.3</v>
       </c>
       <c r="AB187" s="9" t="b">
         <v>0</v>
@@ -18808,90 +18808,90 @@
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>Essex Property Trust, Inc.</t>
+          <t>Garmin Ltd.</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="D188" s="8" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="E188" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="F188" s="7" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="G188" s="8" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="H188" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="I188" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="J188" s="8" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="K188" s="6" t="n">
-        <v>83.3</v>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D188" s="11" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E188" s="8" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F188" s="8" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="G188" s="6" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="H188" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="I188" s="6" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="J188" s="7" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="K188" s="7" t="n">
+        <v>27.7</v>
       </c>
       <c r="L188" s="8" t="n">
         <v>53</v>
       </c>
       <c r="M188" s="9" t="n">
-        <v>62.95</v>
+        <v>63.15</v>
       </c>
       <c r="N188" s="9" t="n">
-        <v>73.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="O188" s="9" t="n">
         <v>186</v>
       </c>
       <c r="P188" s="10" t="n">
-        <v>12</v>
+        <v>6.45</v>
       </c>
       <c r="Q188" s="10" t="n">
-        <v>10.57</v>
+        <v>12.58</v>
       </c>
       <c r="R188" s="10" t="n">
-        <v>6.27</v>
+        <v>7.39</v>
       </c>
       <c r="S188" s="10" t="n">
-        <v>8.52</v>
+        <v>11.4</v>
       </c>
       <c r="T188" s="10" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="U188" s="10" t="n">
-        <v>1.63</v>
+        <v>6.41</v>
       </c>
       <c r="V188" s="10" t="n">
-        <v>2.83</v>
+        <v>2.17</v>
       </c>
       <c r="W188" s="10" t="n">
-        <v>4.17</v>
+        <v>1.38</v>
       </c>
       <c r="X188" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y188" s="9" t="n">
-        <v>20.4</v>
+        <v>0</v>
       </c>
       <c r="Z188" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA188" s="9" t="n">
-        <v>21.3</v>
+        <v>0</v>
       </c>
       <c r="AB188" s="9" t="b">
         <v>0</v>
@@ -20728,90 +20728,90 @@
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>Healthpeak Properties, Inc.</t>
+          <t>Fair Isaac Corporation</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D208" s="8" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="E208" s="7" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="F208" s="7" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="G208" s="6" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="H208" s="11" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="I208" s="8" t="n">
-        <v>53</v>
+        <v>59</v>
+      </c>
+      <c r="E208" s="6" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="F208" s="8" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="G208" s="11" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H208" s="7" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="I208" s="11" t="n">
+        <v>37.9</v>
       </c>
       <c r="J208" s="6" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="K208" s="11" t="n">
-        <v>13.3</v>
+        <v>86.3</v>
+      </c>
+      <c r="K208" s="8" t="n">
+        <v>53.4</v>
       </c>
       <c r="L208" s="8" t="n">
         <v>52.2</v>
       </c>
       <c r="M208" s="9" t="n">
-        <v>58.96</v>
+        <v>58.76</v>
       </c>
       <c r="N208" s="9" t="n">
-        <v>66.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="O208" s="9" t="n">
         <v>207</v>
       </c>
       <c r="P208" s="10" t="n">
-        <v>13.1</v>
+        <v>12.98</v>
       </c>
       <c r="Q208" s="10" t="n">
-        <v>9.789999999999999</v>
+        <v>15.71</v>
       </c>
       <c r="R208" s="10" t="n">
-        <v>6.03</v>
+        <v>7.65</v>
       </c>
       <c r="S208" s="10" t="n">
-        <v>10.72</v>
+        <v>1</v>
       </c>
       <c r="T208" s="10" t="n">
-        <v>2.81</v>
+        <v>4.13</v>
       </c>
       <c r="U208" s="10" t="n">
-        <v>5.3</v>
+        <v>3.79</v>
       </c>
       <c r="V208" s="10" t="n">
-        <v>3.83</v>
+        <v>4.32</v>
       </c>
       <c r="W208" s="10" t="n">
-        <v>0.67</v>
+        <v>2.67</v>
       </c>
       <c r="X208" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y208" s="9" t="n">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="Z208" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA208" s="9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB208" s="9" t="b">
         <v>0</v>
@@ -20824,90 +20824,90 @@
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>Fair Isaac Corporation</t>
+          <t>Healthpeak Properties, Inc.</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D209" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="E209" s="6" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="F209" s="8" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="G209" s="11" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="H209" s="7" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="I209" s="11" t="n">
-        <v>37.9</v>
+        <v>59.5</v>
+      </c>
+      <c r="E209" s="7" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F209" s="7" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="G209" s="6" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="H209" s="11" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I209" s="8" t="n">
+        <v>53</v>
       </c>
       <c r="J209" s="6" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="K209" s="8" t="n">
-        <v>53.4</v>
+        <v>76.7</v>
+      </c>
+      <c r="K209" s="11" t="n">
+        <v>13.3</v>
       </c>
       <c r="L209" s="8" t="n">
         <v>52.2</v>
       </c>
       <c r="M209" s="9" t="n">
-        <v>58.76</v>
+        <v>58.96</v>
       </c>
       <c r="N209" s="9" t="n">
-        <v>64.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="O209" s="9" t="n">
         <v>207</v>
       </c>
       <c r="P209" s="10" t="n">
-        <v>12.98</v>
+        <v>13.1</v>
       </c>
       <c r="Q209" s="10" t="n">
-        <v>15.71</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="R209" s="10" t="n">
-        <v>7.65</v>
+        <v>6.03</v>
       </c>
       <c r="S209" s="10" t="n">
-        <v>1</v>
+        <v>10.72</v>
       </c>
       <c r="T209" s="10" t="n">
-        <v>4.13</v>
+        <v>2.81</v>
       </c>
       <c r="U209" s="10" t="n">
-        <v>3.79</v>
+        <v>5.3</v>
       </c>
       <c r="V209" s="10" t="n">
-        <v>4.32</v>
+        <v>3.83</v>
       </c>
       <c r="W209" s="10" t="n">
-        <v>2.67</v>
+        <v>0.67</v>
       </c>
       <c r="X209" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y209" s="9" t="n">
-        <v>28.9</v>
+        <v>0</v>
       </c>
       <c r="Z209" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA209" s="9" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB209" s="9" t="b">
         <v>0</v>
@@ -21976,78 +21976,78 @@
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>EXR</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Extra Space Storage Inc</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="D221" s="11" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E221" s="6" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="F221" s="6" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="G221" s="6" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="H221" s="8" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="I221" s="7" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="J221" s="11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="K221" s="11" t="n">
-        <v>8.800000000000001</v>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D221" s="8" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="E221" s="7" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="F221" s="8" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G221" s="7" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="H221" s="7" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="I221" s="8" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="J221" s="7" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="K221" s="8" t="n">
+        <v>63.3</v>
       </c>
       <c r="L221" s="8" t="n">
         <v>51.5</v>
       </c>
       <c r="M221" s="9" t="n">
-        <v>56.18</v>
+        <v>56.37</v>
       </c>
       <c r="N221" s="9" t="n">
-        <v>61</v>
+        <v>86.3</v>
       </c>
       <c r="O221" s="9" t="n">
         <v>220</v>
       </c>
       <c r="P221" s="10" t="n">
-        <v>2.82</v>
+        <v>13.77</v>
       </c>
       <c r="Q221" s="10" t="n">
-        <v>15.36</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="R221" s="10" t="n">
-        <v>9.68</v>
+        <v>7.47</v>
       </c>
       <c r="S221" s="10" t="n">
-        <v>11.95</v>
+        <v>5.61</v>
       </c>
       <c r="T221" s="10" t="n">
-        <v>5.59</v>
+        <v>4.29</v>
       </c>
       <c r="U221" s="10" t="n">
-        <v>4.48</v>
+        <v>5.34</v>
       </c>
       <c r="V221" s="10" t="n">
-        <v>1.18</v>
+        <v>2.33</v>
       </c>
       <c r="W221" s="10" t="n">
-        <v>0.44</v>
+        <v>3.17</v>
       </c>
       <c r="X221" s="9" t="b">
         <v>0</v>
@@ -22056,10 +22056,10 @@
         <v>0</v>
       </c>
       <c r="Z221" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA221" s="9" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AB221" s="9" t="b">
         <v>0</v>
@@ -22072,78 +22072,78 @@
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>EXR</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>Extra Space Storage Inc</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="D222" s="8" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="E222" s="7" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="F222" s="8" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="G222" s="7" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="H222" s="7" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="I222" s="8" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="J222" s="7" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="K222" s="8" t="n">
-        <v>63.3</v>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D222" s="11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E222" s="6" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F222" s="6" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="G222" s="6" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="H222" s="8" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="I222" s="7" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="J222" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="K222" s="11" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="L222" s="8" t="n">
         <v>51.5</v>
       </c>
       <c r="M222" s="9" t="n">
-        <v>56.37</v>
+        <v>56.18</v>
       </c>
       <c r="N222" s="9" t="n">
-        <v>86.3</v>
+        <v>61</v>
       </c>
       <c r="O222" s="9" t="n">
         <v>220</v>
       </c>
       <c r="P222" s="10" t="n">
-        <v>13.77</v>
+        <v>2.82</v>
       </c>
       <c r="Q222" s="10" t="n">
-        <v>9.529999999999999</v>
+        <v>15.36</v>
       </c>
       <c r="R222" s="10" t="n">
-        <v>7.47</v>
+        <v>9.68</v>
       </c>
       <c r="S222" s="10" t="n">
-        <v>5.61</v>
+        <v>11.95</v>
       </c>
       <c r="T222" s="10" t="n">
-        <v>4.29</v>
+        <v>5.59</v>
       </c>
       <c r="U222" s="10" t="n">
-        <v>5.34</v>
+        <v>4.48</v>
       </c>
       <c r="V222" s="10" t="n">
-        <v>2.33</v>
+        <v>1.18</v>
       </c>
       <c r="W222" s="10" t="n">
-        <v>3.17</v>
+        <v>0.44</v>
       </c>
       <c r="X222" s="9" t="b">
         <v>0</v>
@@ -22152,10 +22152,10 @@
         <v>0</v>
       </c>
       <c r="Z222" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA222" s="9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AB222" s="9" t="b">
         <v>0</v>
@@ -22168,90 +22168,90 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D223" s="8" t="n">
-        <v>57.4</v>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D223" s="7" t="n">
+        <v>41.4</v>
       </c>
       <c r="E223" s="7" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="F223" s="8" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="G223" s="11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H223" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="I223" s="6" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="J223" s="8" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="K223" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>39.7</v>
+      </c>
+      <c r="F223" s="6" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="G223" s="8" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="H223" s="6" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="I223" s="7" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="J223" s="7" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="K223" s="6" t="n">
+        <v>84.90000000000001</v>
       </c>
       <c r="L223" s="8" t="n">
         <v>51.5</v>
       </c>
       <c r="M223" s="9" t="n">
-        <v>55.78</v>
+        <v>55.98</v>
       </c>
       <c r="N223" s="9" t="n">
-        <v>76.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O223" s="9" t="n">
         <v>222</v>
       </c>
       <c r="P223" s="10" t="n">
-        <v>12.62</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Q223" s="10" t="n">
-        <v>9.07</v>
+        <v>8.74</v>
       </c>
       <c r="R223" s="10" t="n">
-        <v>8.220000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="S223" s="10" t="n">
-        <v>2.31</v>
+        <v>6.85</v>
       </c>
       <c r="T223" s="10" t="n">
-        <v>5.7</v>
+        <v>7.81</v>
       </c>
       <c r="U223" s="10" t="n">
-        <v>6.62</v>
+        <v>4.36</v>
       </c>
       <c r="V223" s="10" t="n">
-        <v>3.35</v>
+        <v>1.78</v>
       </c>
       <c r="W223" s="10" t="n">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="X223" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y223" s="9" t="n">
-        <v>15.9</v>
+        <v>0</v>
       </c>
       <c r="Z223" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA223" s="9" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="AB223" s="9" t="b">
         <v>0</v>
@@ -22264,90 +22264,90 @@
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D224" s="7" t="n">
-        <v>41.4</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D224" s="8" t="n">
+        <v>57.4</v>
       </c>
       <c r="E224" s="7" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="F224" s="6" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="G224" s="8" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="H224" s="6" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="I224" s="7" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="J224" s="7" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="K224" s="6" t="n">
-        <v>84.90000000000001</v>
+        <v>41.2</v>
+      </c>
+      <c r="F224" s="8" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G224" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H224" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="I224" s="6" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="J224" s="8" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="K224" s="8" t="n">
+        <v>71.59999999999999</v>
       </c>
       <c r="L224" s="8" t="n">
         <v>51.5</v>
       </c>
       <c r="M224" s="9" t="n">
-        <v>55.98</v>
+        <v>55.78</v>
       </c>
       <c r="N224" s="9" t="n">
-        <v>75.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O224" s="9" t="n">
         <v>222</v>
       </c>
       <c r="P224" s="10" t="n">
-        <v>9.119999999999999</v>
+        <v>12.62</v>
       </c>
       <c r="Q224" s="10" t="n">
-        <v>8.74</v>
+        <v>9.07</v>
       </c>
       <c r="R224" s="10" t="n">
-        <v>8.57</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="S224" s="10" t="n">
-        <v>6.85</v>
+        <v>2.31</v>
       </c>
       <c r="T224" s="10" t="n">
-        <v>7.81</v>
+        <v>5.7</v>
       </c>
       <c r="U224" s="10" t="n">
-        <v>4.36</v>
+        <v>6.62</v>
       </c>
       <c r="V224" s="10" t="n">
-        <v>1.78</v>
+        <v>3.35</v>
       </c>
       <c r="W224" s="10" t="n">
-        <v>4.25</v>
+        <v>3.58</v>
       </c>
       <c r="X224" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y224" s="9" t="n">
-        <v>0</v>
+        <v>15.9</v>
       </c>
       <c r="Z224" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA224" s="9" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="AB224" s="9" t="b">
         <v>0</v>
@@ -23992,90 +23992,90 @@
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>Walt Disney Company (The)</t>
+          <t>Humana Inc.</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="D242" s="7" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="E242" s="11" t="n">
-        <v>34</v>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="D242" s="8" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="E242" s="7" t="n">
+        <v>40</v>
       </c>
       <c r="F242" s="6" t="n">
-        <v>66.7</v>
+        <v>70.7</v>
       </c>
       <c r="G242" s="8" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="H242" s="6" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="I242" s="6" t="n">
-        <v>65</v>
+        <v>67.09999999999999</v>
+      </c>
+      <c r="H242" s="11" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I242" s="8" t="n">
+        <v>57.4</v>
       </c>
       <c r="J242" s="7" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="K242" s="7" t="n">
-        <v>45.8</v>
+        <v>49.2</v>
+      </c>
+      <c r="K242" s="11" t="n">
+        <v>10.2</v>
       </c>
       <c r="L242" s="8" t="n">
         <v>51</v>
       </c>
       <c r="M242" s="9" t="n">
-        <v>51.99</v>
+        <v>52.19</v>
       </c>
       <c r="N242" s="9" t="n">
-        <v>78.5</v>
+        <v>62.9</v>
       </c>
       <c r="O242" s="9" t="n">
         <v>241</v>
       </c>
       <c r="P242" s="10" t="n">
-        <v>10.65</v>
+        <v>14.12</v>
       </c>
       <c r="Q242" s="10" t="n">
-        <v>7.47</v>
+        <v>8.81</v>
       </c>
       <c r="R242" s="10" t="n">
-        <v>8.67</v>
+        <v>9.19</v>
       </c>
       <c r="S242" s="10" t="n">
-        <v>6.96</v>
+        <v>8.73</v>
       </c>
       <c r="T242" s="10" t="n">
-        <v>6.96</v>
+        <v>1.43</v>
       </c>
       <c r="U242" s="10" t="n">
-        <v>6.5</v>
+        <v>5.74</v>
       </c>
       <c r="V242" s="10" t="n">
-        <v>1.46</v>
+        <v>2.46</v>
       </c>
       <c r="W242" s="10" t="n">
-        <v>2.29</v>
+        <v>0.51</v>
       </c>
       <c r="X242" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y242" s="9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Z242" s="9" t="b">
         <v>1</v>
       </c>
       <c r="AA242" s="9" t="n">
-        <v>10.4</v>
+        <v>8.9</v>
       </c>
       <c r="AB242" s="9" t="b">
         <v>0</v>
@@ -24088,90 +24088,90 @@
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>Humana Inc.</t>
+          <t>Walt Disney Company (The)</t>
         </is>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="D243" s="8" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="E243" s="7" t="n">
-        <v>40</v>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D243" s="7" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="E243" s="11" t="n">
+        <v>34</v>
       </c>
       <c r="F243" s="6" t="n">
-        <v>70.7</v>
+        <v>66.7</v>
       </c>
       <c r="G243" s="8" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="H243" s="11" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I243" s="8" t="n">
-        <v>57.4</v>
+        <v>53.5</v>
+      </c>
+      <c r="H243" s="6" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="I243" s="6" t="n">
+        <v>65</v>
       </c>
       <c r="J243" s="7" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="K243" s="11" t="n">
-        <v>10.2</v>
+        <v>29.2</v>
+      </c>
+      <c r="K243" s="7" t="n">
+        <v>45.8</v>
       </c>
       <c r="L243" s="8" t="n">
         <v>51</v>
       </c>
       <c r="M243" s="9" t="n">
-        <v>52.19</v>
+        <v>51.99</v>
       </c>
       <c r="N243" s="9" t="n">
-        <v>62.9</v>
+        <v>78.5</v>
       </c>
       <c r="O243" s="9" t="n">
         <v>241</v>
       </c>
       <c r="P243" s="10" t="n">
-        <v>14.12</v>
+        <v>10.65</v>
       </c>
       <c r="Q243" s="10" t="n">
-        <v>8.81</v>
+        <v>7.47</v>
       </c>
       <c r="R243" s="10" t="n">
-        <v>9.19</v>
+        <v>8.67</v>
       </c>
       <c r="S243" s="10" t="n">
-        <v>8.73</v>
+        <v>6.96</v>
       </c>
       <c r="T243" s="10" t="n">
-        <v>1.43</v>
+        <v>6.96</v>
       </c>
       <c r="U243" s="10" t="n">
-        <v>5.74</v>
+        <v>6.5</v>
       </c>
       <c r="V243" s="10" t="n">
-        <v>2.46</v>
+        <v>1.46</v>
       </c>
       <c r="W243" s="10" t="n">
-        <v>0.51</v>
+        <v>2.29</v>
       </c>
       <c r="X243" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y243" s="9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Z243" s="9" t="b">
         <v>1</v>
       </c>
       <c r="AA243" s="9" t="n">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="AB243" s="9" t="b">
         <v>0</v>
@@ -24760,90 +24760,90 @@
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>Westinghouse Air Brake Technolo</t>
+          <t>Tyson Foods, Inc.</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D250" s="11" t="n">
-        <v>29.5</v>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D250" s="8" t="n">
+        <v>65.2</v>
       </c>
       <c r="E250" s="11" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="F250" s="6" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="G250" s="6" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="H250" s="6" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="I250" s="7" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="J250" s="7" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="K250" s="11" t="n">
-        <v>21</v>
+        <v>29.2</v>
+      </c>
+      <c r="F250" s="7" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="G250" s="7" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="H250" s="8" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="I250" s="8" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="J250" s="6" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="K250" s="6" t="n">
+        <v>76.5</v>
       </c>
       <c r="L250" s="8" t="n">
         <v>50.7</v>
       </c>
       <c r="M250" s="9" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="N250" s="9" t="n">
-        <v>70.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="O250" s="9" t="n">
         <v>249</v>
       </c>
       <c r="P250" s="10" t="n">
-        <v>6.49</v>
+        <v>14.35</v>
       </c>
       <c r="Q250" s="10" t="n">
-        <v>7.42</v>
+        <v>6.43</v>
       </c>
       <c r="R250" s="10" t="n">
-        <v>10.23</v>
+        <v>4.78</v>
       </c>
       <c r="S250" s="10" t="n">
-        <v>10.91</v>
+        <v>5.31</v>
       </c>
       <c r="T250" s="10" t="n">
-        <v>7.16</v>
+        <v>5.63</v>
       </c>
       <c r="U250" s="10" t="n">
-        <v>4.91</v>
+        <v>6.28</v>
       </c>
       <c r="V250" s="10" t="n">
-        <v>2.56</v>
+        <v>4.12</v>
       </c>
       <c r="W250" s="10" t="n">
-        <v>1.05</v>
+        <v>3.82</v>
       </c>
       <c r="X250" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y250" s="9" t="n">
-        <v>3.7</v>
+        <v>7.7</v>
       </c>
       <c r="Z250" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA250" s="9" t="n">
-        <v>20.9</v>
+        <v>9.6</v>
       </c>
       <c r="AB250" s="9" t="b">
         <v>0</v>
@@ -24856,90 +24856,90 @@
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>TSN</t>
+          <t>WAB</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>Tyson Foods, Inc.</t>
+          <t>Westinghouse Air Brake Technolo</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="D251" s="8" t="n">
-        <v>65.2</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D251" s="11" t="n">
+        <v>29.5</v>
       </c>
       <c r="E251" s="11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="F251" s="7" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="G251" s="7" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="H251" s="8" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="I251" s="8" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="J251" s="6" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="K251" s="6" t="n">
-        <v>76.5</v>
+        <v>33.7</v>
+      </c>
+      <c r="F251" s="6" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="G251" s="6" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="H251" s="6" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="I251" s="7" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="J251" s="7" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="K251" s="11" t="n">
+        <v>21</v>
       </c>
       <c r="L251" s="8" t="n">
         <v>50.7</v>
       </c>
       <c r="M251" s="9" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="N251" s="9" t="n">
-        <v>72.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="O251" s="9" t="n">
         <v>249</v>
       </c>
       <c r="P251" s="10" t="n">
-        <v>14.35</v>
+        <v>6.49</v>
       </c>
       <c r="Q251" s="10" t="n">
-        <v>6.43</v>
+        <v>7.42</v>
       </c>
       <c r="R251" s="10" t="n">
-        <v>4.78</v>
+        <v>10.23</v>
       </c>
       <c r="S251" s="10" t="n">
-        <v>5.31</v>
+        <v>10.91</v>
       </c>
       <c r="T251" s="10" t="n">
-        <v>5.63</v>
+        <v>7.16</v>
       </c>
       <c r="U251" s="10" t="n">
-        <v>6.28</v>
+        <v>4.91</v>
       </c>
       <c r="V251" s="10" t="n">
-        <v>4.12</v>
+        <v>2.56</v>
       </c>
       <c r="W251" s="10" t="n">
-        <v>3.82</v>
+        <v>1.05</v>
       </c>
       <c r="X251" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y251" s="9" t="n">
-        <v>7.7</v>
+        <v>3.7</v>
       </c>
       <c r="Z251" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA251" s="9" t="n">
-        <v>9.6</v>
+        <v>20.9</v>
       </c>
       <c r="AB251" s="9" t="b">
         <v>0</v>
@@ -25816,84 +25816,84 @@
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>Medtronic plc.</t>
+          <t>Motorola Solutions, Inc.</t>
         </is>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D261" s="8" t="n">
-        <v>58.5</v>
+        <v>52.1</v>
       </c>
       <c r="E261" s="7" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="F261" s="8" t="n">
-        <v>52.3</v>
+        <v>44.4</v>
+      </c>
+      <c r="F261" s="7" t="n">
+        <v>47</v>
       </c>
       <c r="G261" s="11" t="n">
-        <v>26.5</v>
+        <v>29.3</v>
       </c>
       <c r="H261" s="6" t="n">
-        <v>76.5</v>
+        <v>93.5</v>
       </c>
       <c r="I261" s="8" t="n">
-        <v>52.6</v>
+        <v>53.6</v>
       </c>
       <c r="J261" s="7" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="K261" s="8" t="n">
-        <v>64.40000000000001</v>
+        <v>49.3</v>
+      </c>
+      <c r="K261" s="7" t="n">
+        <v>37</v>
       </c>
       <c r="L261" s="7" t="n">
         <v>50.2</v>
       </c>
       <c r="M261" s="9" t="n">
-        <v>48.21</v>
+        <v>48.41</v>
       </c>
       <c r="N261" s="9" t="n">
-        <v>75.5</v>
+        <v>74</v>
       </c>
       <c r="O261" s="9" t="n">
         <v>260</v>
       </c>
       <c r="P261" s="10" t="n">
-        <v>12.88</v>
+        <v>11.47</v>
       </c>
       <c r="Q261" s="10" t="n">
-        <v>9.57</v>
+        <v>9.77</v>
       </c>
       <c r="R261" s="10" t="n">
-        <v>6.81</v>
+        <v>6.11</v>
       </c>
       <c r="S261" s="10" t="n">
-        <v>3.45</v>
+        <v>3.81</v>
       </c>
       <c r="T261" s="10" t="n">
-        <v>7.65</v>
+        <v>9.35</v>
       </c>
       <c r="U261" s="10" t="n">
-        <v>5.26</v>
+        <v>5.36</v>
       </c>
       <c r="V261" s="10" t="n">
-        <v>1.36</v>
+        <v>2.47</v>
       </c>
       <c r="W261" s="10" t="n">
-        <v>3.22</v>
+        <v>1.85</v>
       </c>
       <c r="X261" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y261" s="9" t="n">
-        <v>7.3</v>
+        <v>4.6</v>
       </c>
       <c r="Z261" s="9" t="b">
         <v>0</v>
@@ -25912,84 +25912,84 @@
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>Motorola Solutions, Inc.</t>
+          <t>Medtronic plc.</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D262" s="8" t="n">
-        <v>52.1</v>
+        <v>58.5</v>
       </c>
       <c r="E262" s="7" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="F262" s="7" t="n">
-        <v>47</v>
+        <v>43.5</v>
+      </c>
+      <c r="F262" s="8" t="n">
+        <v>52.3</v>
       </c>
       <c r="G262" s="11" t="n">
-        <v>29.3</v>
+        <v>26.5</v>
       </c>
       <c r="H262" s="6" t="n">
-        <v>93.5</v>
+        <v>76.5</v>
       </c>
       <c r="I262" s="8" t="n">
-        <v>53.6</v>
+        <v>52.6</v>
       </c>
       <c r="J262" s="7" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="K262" s="7" t="n">
-        <v>37</v>
+        <v>27.1</v>
+      </c>
+      <c r="K262" s="8" t="n">
+        <v>64.40000000000001</v>
       </c>
       <c r="L262" s="7" t="n">
         <v>50.2</v>
       </c>
       <c r="M262" s="9" t="n">
-        <v>48.41</v>
+        <v>48.21</v>
       </c>
       <c r="N262" s="9" t="n">
-        <v>74</v>
+        <v>75.5</v>
       </c>
       <c r="O262" s="9" t="n">
         <v>260</v>
       </c>
       <c r="P262" s="10" t="n">
-        <v>11.47</v>
+        <v>12.88</v>
       </c>
       <c r="Q262" s="10" t="n">
-        <v>9.77</v>
+        <v>9.57</v>
       </c>
       <c r="R262" s="10" t="n">
-        <v>6.11</v>
+        <v>6.81</v>
       </c>
       <c r="S262" s="10" t="n">
-        <v>3.81</v>
+        <v>3.45</v>
       </c>
       <c r="T262" s="10" t="n">
-        <v>9.35</v>
+        <v>7.65</v>
       </c>
       <c r="U262" s="10" t="n">
-        <v>5.36</v>
+        <v>5.26</v>
       </c>
       <c r="V262" s="10" t="n">
-        <v>2.47</v>
+        <v>1.36</v>
       </c>
       <c r="W262" s="10" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="X262" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y262" s="9" t="n">
-        <v>4.6</v>
+        <v>7.3</v>
       </c>
       <c r="Z262" s="9" t="b">
         <v>0</v>
@@ -28312,42 +28312,42 @@
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
         <is>
-          <t>American Electric Power Company</t>
+          <t>O'Reilly Automotive, Inc.</t>
         </is>
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D287" s="8" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="E287" s="8" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="F287" s="7" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="G287" s="6" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="H287" s="8" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="I287" s="11" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="J287" s="11" t="n">
-        <v>16.1</v>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D287" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="E287" s="6" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="F287" s="8" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="G287" s="7" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="H287" s="6" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="I287" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="J287" s="7" t="n">
+        <v>32.6</v>
       </c>
       <c r="K287" s="7" t="n">
-        <v>25.8</v>
+        <v>31.9</v>
       </c>
       <c r="L287" s="7" t="n">
         <v>49.4</v>
@@ -28356,46 +28356,46 @@
         <v>43.23</v>
       </c>
       <c r="N287" s="9" t="n">
-        <v>70.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O287" s="9" t="n">
         <v>286</v>
       </c>
       <c r="P287" s="10" t="n">
-        <v>11.57</v>
+        <v>5.94</v>
       </c>
       <c r="Q287" s="10" t="n">
-        <v>11.19</v>
+        <v>15.31</v>
       </c>
       <c r="R287" s="10" t="n">
-        <v>6.47</v>
+        <v>6.87</v>
       </c>
       <c r="S287" s="10" t="n">
-        <v>9.92</v>
+        <v>5.77</v>
       </c>
       <c r="T287" s="10" t="n">
-        <v>5.44</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="U287" s="10" t="n">
-        <v>2.68</v>
+        <v>3.9</v>
       </c>
       <c r="V287" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.63</v>
       </c>
       <c r="W287" s="10" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="X287" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y287" s="9" t="n">
-        <v>12</v>
+        <v>2.3</v>
       </c>
       <c r="Z287" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA287" s="9" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="AB287" s="9" t="b">
         <v>0</v>
@@ -28408,42 +28408,42 @@
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Company (The)</t>
+          <t>American Electric Power Company</t>
         </is>
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="D288" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="E288" s="6" t="n">
-        <v>67</v>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D288" s="8" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="E288" s="8" t="n">
+        <v>50.9</v>
       </c>
       <c r="F288" s="7" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="G288" s="7" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H288" s="6" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="I288" s="7" t="n">
-        <v>43.4</v>
+        <v>49.8</v>
+      </c>
+      <c r="G288" s="6" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="H288" s="8" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I288" s="11" t="n">
+        <v>26.8</v>
       </c>
       <c r="J288" s="11" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K288" s="8" t="n">
-        <v>55.9</v>
+        <v>16.1</v>
+      </c>
+      <c r="K288" s="7" t="n">
+        <v>25.8</v>
       </c>
       <c r="L288" s="7" t="n">
         <v>49.4</v>
@@ -28452,46 +28452,46 @@
         <v>43.03</v>
       </c>
       <c r="N288" s="9" t="n">
-        <v>71</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O288" s="9" t="n">
         <v>287</v>
       </c>
       <c r="P288" s="10" t="n">
-        <v>9.9</v>
+        <v>11.57</v>
       </c>
       <c r="Q288" s="10" t="n">
-        <v>14.75</v>
+        <v>11.19</v>
       </c>
       <c r="R288" s="10" t="n">
-        <v>5.25</v>
+        <v>6.47</v>
       </c>
       <c r="S288" s="10" t="n">
-        <v>4.09</v>
+        <v>9.92</v>
       </c>
       <c r="T288" s="10" t="n">
-        <v>7.65</v>
+        <v>5.44</v>
       </c>
       <c r="U288" s="10" t="n">
-        <v>4.34</v>
+        <v>2.68</v>
       </c>
       <c r="V288" s="10" t="n">
-        <v>0.59</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W288" s="10" t="n">
-        <v>2.79</v>
+        <v>1.29</v>
       </c>
       <c r="X288" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y288" s="9" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="Z288" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA288" s="9" t="n">
-        <v>1.2</v>
+        <v>13.5</v>
       </c>
       <c r="AB288" s="9" t="b">
         <v>0</v>
@@ -28504,90 +28504,90 @@
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
-          <t>Yum! Brands, Inc.</t>
+          <t>Procter &amp; Gamble Company (The)</t>
         </is>
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D289" s="7" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="E289" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="E289" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="F289" s="7" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="G289" s="7" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H289" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="I289" s="7" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="J289" s="11" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K289" s="8" t="n">
         <v>55.9</v>
       </c>
-      <c r="F289" s="11" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="G289" s="8" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="H289" s="6" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="I289" s="7" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="J289" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="K289" s="11" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L289" s="7" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="M289" s="9" t="n">
         <v>42.83</v>
       </c>
       <c r="N289" s="9" t="n">
-        <v>61.7</v>
+        <v>71</v>
       </c>
       <c r="O289" s="9" t="n">
         <v>288</v>
       </c>
       <c r="P289" s="10" t="n">
-        <v>8.19</v>
+        <v>9.9</v>
       </c>
       <c r="Q289" s="10" t="n">
-        <v>12.3</v>
+        <v>14.75</v>
       </c>
       <c r="R289" s="10" t="n">
-        <v>4.49</v>
+        <v>5.25</v>
       </c>
       <c r="S289" s="10" t="n">
-        <v>7.58</v>
+        <v>4.09</v>
       </c>
       <c r="T289" s="10" t="n">
-        <v>9.42</v>
+        <v>7.65</v>
       </c>
       <c r="U289" s="10" t="n">
-        <v>4.59</v>
+        <v>4.34</v>
       </c>
       <c r="V289" s="10" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="W289" s="10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="X289" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y289" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="W289" s="10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="X289" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y289" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="Z289" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA289" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB289" s="9" t="b">
         <v>0</v>
@@ -28600,90 +28600,90 @@
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>Equifax, Inc.</t>
+          <t>Yum! Brands, Inc.</t>
         </is>
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D290" s="8" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="E290" s="7" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F290" s="6" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="G290" s="11" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H290" s="11" t="n">
-        <v>29.3</v>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D290" s="7" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E290" s="8" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F290" s="11" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G290" s="8" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="H290" s="6" t="n">
+        <v>94.2</v>
       </c>
       <c r="I290" s="7" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="J290" s="8" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="K290" s="6" t="n">
-        <v>75.3</v>
+        <v>45.9</v>
+      </c>
+      <c r="J290" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K290" s="11" t="n">
+        <v>4.3</v>
       </c>
       <c r="L290" s="7" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="M290" s="9" t="n">
         <v>42.63</v>
       </c>
       <c r="N290" s="9" t="n">
-        <v>70</v>
+        <v>61.7</v>
       </c>
       <c r="O290" s="9" t="n">
         <v>289</v>
       </c>
       <c r="P290" s="10" t="n">
-        <v>13.37</v>
+        <v>8.19</v>
       </c>
       <c r="Q290" s="10" t="n">
-        <v>10.31</v>
+        <v>12.3</v>
       </c>
       <c r="R290" s="10" t="n">
-        <v>9.699999999999999</v>
+        <v>4.49</v>
       </c>
       <c r="S290" s="10" t="n">
-        <v>1.57</v>
+        <v>7.58</v>
       </c>
       <c r="T290" s="10" t="n">
-        <v>2.93</v>
+        <v>9.42</v>
       </c>
       <c r="U290" s="10" t="n">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="V290" s="10" t="n">
-        <v>3.66</v>
+        <v>2.5</v>
       </c>
       <c r="W290" s="10" t="n">
-        <v>3.77</v>
+        <v>0.21</v>
       </c>
       <c r="X290" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y290" s="9" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="Z290" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA290" s="9" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AB290" s="9" t="b">
         <v>0</v>
@@ -28696,42 +28696,42 @@
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>O'Reilly Automotive, Inc.</t>
+          <t>Equifax, Inc.</t>
         </is>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D291" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="E291" s="6" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="F291" s="8" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="G291" s="7" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="H291" s="6" t="n">
-        <v>83.90000000000001</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D291" s="8" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="E291" s="7" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="F291" s="6" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="G291" s="11" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H291" s="11" t="n">
+        <v>29.3</v>
       </c>
       <c r="I291" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="J291" s="7" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="K291" s="7" t="n">
-        <v>31.9</v>
+        <v>39.4</v>
+      </c>
+      <c r="J291" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="K291" s="6" t="n">
+        <v>75.3</v>
       </c>
       <c r="L291" s="7" t="n">
         <v>49.2</v>
@@ -28740,46 +28740,46 @@
         <v>42.43</v>
       </c>
       <c r="N291" s="9" t="n">
-        <v>66.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="O291" s="9" t="n">
         <v>290</v>
       </c>
       <c r="P291" s="10" t="n">
-        <v>5.94</v>
+        <v>13.37</v>
       </c>
       <c r="Q291" s="10" t="n">
-        <v>15.31</v>
+        <v>10.31</v>
       </c>
       <c r="R291" s="10" t="n">
-        <v>6.71</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S291" s="10" t="n">
-        <v>5.77</v>
+        <v>1.57</v>
       </c>
       <c r="T291" s="10" t="n">
-        <v>8.390000000000001</v>
+        <v>2.93</v>
       </c>
       <c r="U291" s="10" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="V291" s="10" t="n">
-        <v>1.63</v>
+        <v>3.66</v>
       </c>
       <c r="W291" s="10" t="n">
-        <v>1.6</v>
+        <v>3.77</v>
       </c>
       <c r="X291" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y291" s="9" t="n">
-        <v>2.3</v>
+        <v>23.5</v>
       </c>
       <c r="Z291" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA291" s="9" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB291" s="9" t="b">
         <v>0</v>
@@ -28792,12 +28792,12 @@
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
         <is>
-          <t>Old Dominion Freight Line, Inc.</t>
+          <t>Pentair plc.</t>
         </is>
       </c>
       <c r="C292" s="5" t="inlineStr">
@@ -28805,77 +28805,77 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D292" s="11" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E292" s="6" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="F292" s="11" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="G292" s="8" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="H292" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="I292" s="8" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="J292" s="8" t="n">
-        <v>57.3</v>
+      <c r="D292" s="6" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="E292" s="7" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="F292" s="7" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="G292" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H292" s="11" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I292" s="11" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="J292" s="6" t="n">
+        <v>97.59999999999999</v>
       </c>
       <c r="K292" s="8" t="n">
-        <v>61.7</v>
+        <v>60.5</v>
       </c>
       <c r="L292" s="7" t="n">
         <v>49.2</v>
       </c>
       <c r="M292" s="9" t="n">
-        <v>42.23</v>
+        <v>42.03</v>
       </c>
       <c r="N292" s="9" t="n">
-        <v>75.40000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="O292" s="9" t="n">
         <v>291</v>
       </c>
       <c r="P292" s="10" t="n">
-        <v>5.78</v>
+        <v>19.01</v>
       </c>
       <c r="Q292" s="10" t="n">
-        <v>16.25</v>
+        <v>10.64</v>
       </c>
       <c r="R292" s="10" t="n">
-        <v>4.31</v>
+        <v>4.85</v>
       </c>
       <c r="S292" s="10" t="n">
-        <v>7.89</v>
+        <v>0.39</v>
       </c>
       <c r="T292" s="10" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="U292" s="10" t="n">
-        <v>5.91</v>
+        <v>3.68</v>
       </c>
       <c r="V292" s="10" t="n">
-        <v>2.87</v>
+        <v>4.88</v>
       </c>
       <c r="W292" s="10" t="n">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="X292" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y292" s="9" t="n">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="Z292" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA292" s="9" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AB292" s="9" t="b">
         <v>0</v>
@@ -28888,12 +28888,12 @@
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
         <is>
-          <t>Pentair plc.</t>
+          <t>Old Dominion Freight Line, Inc.</t>
         </is>
       </c>
       <c r="C293" s="5" t="inlineStr">
@@ -28901,77 +28901,77 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D293" s="6" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="E293" s="7" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="F293" s="7" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="G293" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H293" s="11" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="I293" s="11" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="J293" s="6" t="n">
-        <v>97.59999999999999</v>
+      <c r="D293" s="11" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E293" s="6" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="F293" s="11" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="G293" s="8" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="H293" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="I293" s="8" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="J293" s="8" t="n">
+        <v>57.3</v>
       </c>
       <c r="K293" s="8" t="n">
-        <v>60.5</v>
+        <v>61.7</v>
       </c>
       <c r="L293" s="7" t="n">
         <v>49.2</v>
       </c>
       <c r="M293" s="9" t="n">
-        <v>42.03</v>
+        <v>42.23</v>
       </c>
       <c r="N293" s="9" t="n">
-        <v>63.1</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="O293" s="9" t="n">
         <v>291</v>
       </c>
       <c r="P293" s="10" t="n">
-        <v>19.01</v>
+        <v>5.78</v>
       </c>
       <c r="Q293" s="10" t="n">
-        <v>10.64</v>
+        <v>16.25</v>
       </c>
       <c r="R293" s="10" t="n">
-        <v>4.85</v>
+        <v>4.31</v>
       </c>
       <c r="S293" s="10" t="n">
-        <v>0.39</v>
+        <v>7.89</v>
       </c>
       <c r="T293" s="10" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="U293" s="10" t="n">
-        <v>3.68</v>
+        <v>5.91</v>
       </c>
       <c r="V293" s="10" t="n">
-        <v>4.88</v>
+        <v>2.87</v>
       </c>
       <c r="W293" s="10" t="n">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="X293" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y293" s="9" t="n">
-        <v>34.5</v>
+        <v>0</v>
       </c>
       <c r="Z293" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA293" s="9" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AB293" s="9" t="b">
         <v>0</v>
@@ -29752,90 +29752,90 @@
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="B302" s="5" t="inlineStr">
         <is>
-          <t>Hormel Foods Corporation</t>
+          <t>Waste Management, Inc.</t>
         </is>
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="D302" s="8" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="E302" s="11" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="F302" s="11" t="n">
-        <v>29.6</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D302" s="7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="E302" s="7" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="F302" s="8" t="n">
+        <v>59.6</v>
       </c>
       <c r="G302" s="7" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="H302" s="7" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="I302" s="8" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="J302" s="6" t="n">
-        <v>94.09999999999999</v>
+        <v>34.2</v>
+      </c>
+      <c r="H302" s="6" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="I302" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="J302" s="11" t="n">
+        <v>24.4</v>
       </c>
       <c r="K302" s="8" t="n">
-        <v>73.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="L302" s="7" t="n">
         <v>48.8</v>
       </c>
       <c r="M302" s="9" t="n">
-        <v>40.04</v>
+        <v>40.24</v>
       </c>
       <c r="N302" s="9" t="n">
-        <v>67.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="O302" s="9" t="n">
         <v>301</v>
       </c>
       <c r="P302" s="10" t="n">
-        <v>15.07</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="Q302" s="10" t="n">
-        <v>7.14</v>
+        <v>10.59</v>
       </c>
       <c r="R302" s="10" t="n">
-        <v>3.84</v>
+        <v>7.75</v>
       </c>
       <c r="S302" s="10" t="n">
-        <v>5.95</v>
+        <v>4.45</v>
       </c>
       <c r="T302" s="10" t="n">
-        <v>3.11</v>
+        <v>9.19</v>
       </c>
       <c r="U302" s="10" t="n">
-        <v>5.28</v>
+        <v>2.7</v>
       </c>
       <c r="V302" s="10" t="n">
-        <v>4.71</v>
+        <v>1.22</v>
       </c>
       <c r="W302" s="10" t="n">
-        <v>3.68</v>
+        <v>3.52</v>
       </c>
       <c r="X302" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y302" s="9" t="n">
-        <v>4.8</v>
+        <v>11.9</v>
       </c>
       <c r="Z302" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA302" s="9" t="n">
-        <v>7</v>
+        <v>13.3</v>
       </c>
       <c r="AB302" s="9" t="b">
         <v>0</v>
@@ -29848,90 +29848,90 @@
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B303" s="5" t="inlineStr">
         <is>
-          <t>Waste Management, Inc.</t>
+          <t>Hormel Foods Corporation</t>
         </is>
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D303" s="7" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="E303" s="7" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="F303" s="8" t="n">
-        <v>59.6</v>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D303" s="8" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="E303" s="11" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F303" s="11" t="n">
+        <v>29.6</v>
       </c>
       <c r="G303" s="7" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="H303" s="6" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="I303" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="J303" s="11" t="n">
-        <v>24.4</v>
+        <v>45.7</v>
+      </c>
+      <c r="H303" s="7" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I303" s="8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="J303" s="6" t="n">
+        <v>94.09999999999999</v>
       </c>
       <c r="K303" s="8" t="n">
-        <v>70.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="L303" s="7" t="n">
         <v>48.8</v>
       </c>
       <c r="M303" s="9" t="n">
-        <v>40.24</v>
+        <v>40.04</v>
       </c>
       <c r="N303" s="9" t="n">
-        <v>69.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="O303" s="9" t="n">
         <v>301</v>
       </c>
       <c r="P303" s="10" t="n">
-        <v>9.359999999999999</v>
+        <v>15.07</v>
       </c>
       <c r="Q303" s="10" t="n">
-        <v>10.59</v>
+        <v>7.14</v>
       </c>
       <c r="R303" s="10" t="n">
-        <v>7.75</v>
+        <v>3.84</v>
       </c>
       <c r="S303" s="10" t="n">
-        <v>4.45</v>
+        <v>5.95</v>
       </c>
       <c r="T303" s="10" t="n">
-        <v>9.19</v>
+        <v>3.11</v>
       </c>
       <c r="U303" s="10" t="n">
-        <v>2.7</v>
+        <v>5.28</v>
       </c>
       <c r="V303" s="10" t="n">
-        <v>1.22</v>
+        <v>4.71</v>
       </c>
       <c r="W303" s="10" t="n">
-        <v>3.52</v>
+        <v>3.68</v>
       </c>
       <c r="X303" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y303" s="9" t="n">
-        <v>11.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z303" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA303" s="9" t="n">
-        <v>13.3</v>
+        <v>7</v>
       </c>
       <c r="AB303" s="9" t="b">
         <v>0</v>
@@ -29944,42 +29944,42 @@
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>DHI</t>
         </is>
       </c>
       <c r="B304" s="5" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>D.R. Horton, Inc.</t>
         </is>
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D304" s="6" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="E304" s="6" t="n">
-        <v>65.40000000000001</v>
+        <v>83.59999999999999</v>
+      </c>
+      <c r="E304" s="11" t="n">
+        <v>28.7</v>
       </c>
       <c r="F304" s="11" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G304" s="11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H304" s="11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="I304" s="7" t="n">
-        <v>46.5</v>
+        <v>22</v>
+      </c>
+      <c r="G304" s="7" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="H304" s="7" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="I304" s="8" t="n">
+        <v>52.6</v>
       </c>
       <c r="J304" s="8" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="K304" s="7" t="n">
-        <v>44.1</v>
+        <v>52.2</v>
+      </c>
+      <c r="K304" s="8" t="n">
+        <v>72.3</v>
       </c>
       <c r="L304" s="7" t="n">
         <v>48.6</v>
@@ -29988,46 +29988,46 @@
         <v>39.84</v>
       </c>
       <c r="N304" s="9" t="n">
-        <v>64.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="O304" s="9" t="n">
         <v>303</v>
       </c>
       <c r="P304" s="10" t="n">
-        <v>17.96</v>
+        <v>18.39</v>
       </c>
       <c r="Q304" s="10" t="n">
-        <v>14.39</v>
+        <v>6.3</v>
       </c>
       <c r="R304" s="10" t="n">
-        <v>3.57</v>
+        <v>2.87</v>
       </c>
       <c r="S304" s="10" t="n">
-        <v>0.53</v>
+        <v>4.96</v>
       </c>
       <c r="T304" s="10" t="n">
-        <v>1.99</v>
+        <v>4.62</v>
       </c>
       <c r="U304" s="10" t="n">
-        <v>4.65</v>
+        <v>5.26</v>
       </c>
       <c r="V304" s="10" t="n">
-        <v>3.31</v>
+        <v>2.61</v>
       </c>
       <c r="W304" s="10" t="n">
-        <v>2.2</v>
+        <v>3.62</v>
       </c>
       <c r="X304" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y304" s="9" t="n">
-        <v>29.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z304" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA304" s="9" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="AB304" s="9" t="b">
         <v>0</v>
@@ -30040,90 +30040,90 @@
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>DHI</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
-          <t>D.R. Horton, Inc.</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D305" s="6" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="E305" s="11" t="n">
-        <v>28.7</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="E305" s="6" t="n">
+        <v>65.40000000000001</v>
       </c>
       <c r="F305" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="G305" s="7" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="H305" s="7" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="I305" s="8" t="n">
-        <v>52.6</v>
+        <v>27.5</v>
+      </c>
+      <c r="G305" s="11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H305" s="11" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I305" s="7" t="n">
+        <v>46.5</v>
       </c>
       <c r="J305" s="8" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="K305" s="8" t="n">
-        <v>72.3</v>
+        <v>66.09999999999999</v>
+      </c>
+      <c r="K305" s="7" t="n">
+        <v>44.1</v>
       </c>
       <c r="L305" s="7" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="M305" s="9" t="n">
         <v>39.64</v>
       </c>
       <c r="N305" s="9" t="n">
-        <v>69.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O305" s="9" t="n">
         <v>304</v>
       </c>
       <c r="P305" s="10" t="n">
-        <v>18.39</v>
+        <v>17.96</v>
       </c>
       <c r="Q305" s="10" t="n">
-        <v>6.3</v>
+        <v>14.39</v>
       </c>
       <c r="R305" s="10" t="n">
-        <v>2.73</v>
+        <v>3.57</v>
       </c>
       <c r="S305" s="10" t="n">
-        <v>4.96</v>
+        <v>0.53</v>
       </c>
       <c r="T305" s="10" t="n">
-        <v>4.62</v>
+        <v>1.99</v>
       </c>
       <c r="U305" s="10" t="n">
-        <v>5.26</v>
+        <v>4.65</v>
       </c>
       <c r="V305" s="10" t="n">
-        <v>2.61</v>
+        <v>3.31</v>
       </c>
       <c r="W305" s="10" t="n">
-        <v>3.62</v>
+        <v>2.2</v>
       </c>
       <c r="X305" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y305" s="9" t="n">
-        <v>8.199999999999999</v>
+        <v>29.3</v>
       </c>
       <c r="Z305" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA305" s="9" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="AB305" s="9" t="b">
         <v>0</v>
@@ -30808,84 +30808,84 @@
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B313" s="5" t="inlineStr">
         <is>
-          <t>Lowe's Companies, Inc.</t>
+          <t>Walmart Inc.</t>
         </is>
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D313" s="8" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="E313" s="8" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="F313" s="11" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="G313" s="11" t="n">
-        <v>28.6</v>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D313" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E313" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F313" s="8" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G313" s="8" t="n">
+        <v>54</v>
       </c>
       <c r="H313" s="8" t="n">
-        <v>67.2</v>
+        <v>57.6</v>
       </c>
       <c r="I313" s="8" t="n">
-        <v>57</v>
+        <v>55.1</v>
       </c>
       <c r="J313" s="11" t="n">
-        <v>17.4</v>
+        <v>2.9</v>
       </c>
       <c r="K313" s="11" t="n">
-        <v>6.4</v>
+        <v>23.5</v>
       </c>
       <c r="L313" s="7" t="n">
         <v>48.3</v>
       </c>
       <c r="M313" s="9" t="n">
-        <v>38.05</v>
+        <v>37.85</v>
       </c>
       <c r="N313" s="9" t="n">
-        <v>61.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O313" s="9" t="n">
         <v>312</v>
       </c>
       <c r="P313" s="10" t="n">
-        <v>15.09</v>
+        <v>4.57</v>
       </c>
       <c r="Q313" s="10" t="n">
-        <v>11.92</v>
+        <v>16.5</v>
       </c>
       <c r="R313" s="10" t="n">
-        <v>3.94</v>
+        <v>7.6</v>
       </c>
       <c r="S313" s="10" t="n">
-        <v>3.72</v>
+        <v>7.02</v>
       </c>
       <c r="T313" s="10" t="n">
-        <v>6.72</v>
+        <v>5.76</v>
       </c>
       <c r="U313" s="10" t="n">
-        <v>5.7</v>
+        <v>5.51</v>
       </c>
       <c r="V313" s="10" t="n">
-        <v>0.87</v>
+        <v>0.15</v>
       </c>
       <c r="W313" s="10" t="n">
-        <v>0.32</v>
+        <v>1.18</v>
       </c>
       <c r="X313" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y313" s="9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Z313" s="9" t="b">
         <v>0</v>
@@ -30894,7 +30894,7 @@
         <v>0</v>
       </c>
       <c r="AB313" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC313" s="9" t="n"/>
       <c r="AD313" s="9" t="b">
@@ -30904,84 +30904,84 @@
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B314" s="5" t="inlineStr">
         <is>
-          <t>Walmart Inc.</t>
+          <t>Lowe's Companies, Inc.</t>
         </is>
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="D314" s="11" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="E314" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="F314" s="8" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="G314" s="8" t="n">
-        <v>54</v>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D314" s="8" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="E314" s="8" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="F314" s="11" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="G314" s="11" t="n">
+        <v>28.6</v>
       </c>
       <c r="H314" s="8" t="n">
-        <v>57.6</v>
+        <v>67.2</v>
       </c>
       <c r="I314" s="8" t="n">
-        <v>55.1</v>
+        <v>57</v>
       </c>
       <c r="J314" s="11" t="n">
-        <v>2.9</v>
+        <v>17.4</v>
       </c>
       <c r="K314" s="11" t="n">
-        <v>23.5</v>
+        <v>6.4</v>
       </c>
       <c r="L314" s="7" t="n">
         <v>48.3</v>
       </c>
       <c r="M314" s="9" t="n">
-        <v>37.85</v>
+        <v>38.05</v>
       </c>
       <c r="N314" s="9" t="n">
-        <v>65.40000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="O314" s="9" t="n">
         <v>312</v>
       </c>
       <c r="P314" s="10" t="n">
-        <v>4.57</v>
+        <v>15.09</v>
       </c>
       <c r="Q314" s="10" t="n">
-        <v>16.5</v>
+        <v>11.92</v>
       </c>
       <c r="R314" s="10" t="n">
-        <v>7.6</v>
+        <v>3.94</v>
       </c>
       <c r="S314" s="10" t="n">
-        <v>7.02</v>
+        <v>3.72</v>
       </c>
       <c r="T314" s="10" t="n">
-        <v>5.76</v>
+        <v>6.72</v>
       </c>
       <c r="U314" s="10" t="n">
-        <v>5.51</v>
+        <v>5.7</v>
       </c>
       <c r="V314" s="10" t="n">
-        <v>0.15</v>
+        <v>0.87</v>
       </c>
       <c r="W314" s="10" t="n">
-        <v>1.18</v>
+        <v>0.32</v>
       </c>
       <c r="X314" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y314" s="9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Z314" s="9" t="b">
         <v>0</v>
@@ -30990,7 +30990,7 @@
         <v>0</v>
       </c>
       <c r="AB314" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC314" s="9" t="n"/>
       <c r="AD314" s="9" t="b">
@@ -32632,193 +32632,193 @@
     <row r="332">
       <c r="A332" s="5" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="B332" s="5" t="inlineStr">
         <is>
-          <t>Northern Trust Corporation</t>
+          <t>United Rentals, Inc.</t>
         </is>
       </c>
       <c r="C332" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D332" s="7" t="n">
-        <v>41.7</v>
+        <v>42.8</v>
       </c>
       <c r="E332" s="7" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="F332" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="G332" s="6" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="H332" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="I332" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J332" s="8" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="K332" s="8" t="n">
-        <v>63.2</v>
+        <v>50</v>
+      </c>
+      <c r="F332" s="6" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="G332" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="H332" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="I332" s="7" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="J332" s="7" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="K332" s="7" t="n">
+        <v>33.3</v>
       </c>
       <c r="L332" s="7" t="n">
         <v>47.5</v>
       </c>
       <c r="M332" s="9" t="n">
-        <v>34.06</v>
+        <v>34.26</v>
       </c>
       <c r="N332" s="9" t="n">
-        <v>67.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="O332" s="9" t="n">
         <v>331</v>
       </c>
       <c r="P332" s="10" t="n">
-        <v>9.18</v>
+        <v>9.42</v>
       </c>
       <c r="Q332" s="10" t="n">
-        <v>8.16</v>
+        <v>11</v>
       </c>
       <c r="R332" s="10" t="n">
-        <v>3.77</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="S332" s="10" t="n">
-        <v>12.08</v>
+        <v>8.31</v>
       </c>
       <c r="T332" s="10" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="U332" s="10" t="n">
-        <v>1.85</v>
+        <v>4.04</v>
       </c>
       <c r="V332" s="10" t="n">
-        <v>3.36</v>
+        <v>2.07</v>
       </c>
       <c r="W332" s="10" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="X332" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y332" s="9" t="n">
-        <v>19.3</v>
+        <v>1.1</v>
       </c>
       <c r="Z332" s="9" t="b">
         <v>1</v>
       </c>
       <c r="AA332" s="9" t="n">
-        <v>22.9</v>
+        <v>7</v>
       </c>
       <c r="AB332" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AC332" s="9" t="n"/>
       <c r="AD332" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="5" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="B333" s="5" t="inlineStr">
         <is>
-          <t>United Rentals, Inc.</t>
+          <t>Northern Trust Corporation</t>
         </is>
       </c>
       <c r="C333" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D333" s="7" t="n">
-        <v>42.8</v>
+        <v>41.7</v>
       </c>
       <c r="E333" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="F333" s="6" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="G333" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="H333" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="I333" s="7" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="J333" s="7" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K333" s="7" t="n">
-        <v>33.3</v>
+        <v>37.1</v>
+      </c>
+      <c r="F333" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="G333" s="6" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="H333" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="I333" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J333" s="8" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="K333" s="8" t="n">
+        <v>63.2</v>
       </c>
       <c r="L333" s="7" t="n">
         <v>47.5</v>
       </c>
       <c r="M333" s="9" t="n">
-        <v>34.26</v>
+        <v>34.06</v>
       </c>
       <c r="N333" s="9" t="n">
-        <v>75.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="O333" s="9" t="n">
         <v>331</v>
       </c>
       <c r="P333" s="10" t="n">
-        <v>9.42</v>
+        <v>9.18</v>
       </c>
       <c r="Q333" s="10" t="n">
-        <v>11</v>
+        <v>8.16</v>
       </c>
       <c r="R333" s="10" t="n">
-        <v>8.529999999999999</v>
+        <v>3.77</v>
       </c>
       <c r="S333" s="10" t="n">
-        <v>8.31</v>
+        <v>12.08</v>
       </c>
       <c r="T333" s="10" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="U333" s="10" t="n">
-        <v>4.04</v>
+        <v>1.85</v>
       </c>
       <c r="V333" s="10" t="n">
-        <v>2.07</v>
+        <v>3.36</v>
       </c>
       <c r="W333" s="10" t="n">
-        <v>1.67</v>
+        <v>3.16</v>
       </c>
       <c r="X333" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y333" s="9" t="n">
-        <v>1.1</v>
+        <v>19.3</v>
       </c>
       <c r="Z333" s="9" t="b">
         <v>1</v>
       </c>
       <c r="AA333" s="9" t="n">
-        <v>7</v>
+        <v>22.9</v>
       </c>
       <c r="AB333" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AC333" s="9" t="n"/>
       <c r="AD333" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -33016,12 +33016,12 @@
     <row r="336">
       <c r="A336" s="5" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B336" s="5" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Applied Materials, Inc.</t>
         </is>
       </c>
       <c r="C336" s="5" t="inlineStr">
@@ -33030,64 +33030,64 @@
         </is>
       </c>
       <c r="D336" s="11" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E336" s="6" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="F336" s="8" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="G336" s="8" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="H336" s="11" t="n">
-        <v>26.2</v>
+        <v>30.4</v>
+      </c>
+      <c r="E336" s="8" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="F336" s="7" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="G336" s="6" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="H336" s="7" t="n">
+        <v>32.3</v>
       </c>
       <c r="I336" s="7" t="n">
-        <v>44.4</v>
+        <v>49.2</v>
       </c>
       <c r="J336" s="11" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="K336" s="8" t="n">
-        <v>49.3</v>
+        <v>16.4</v>
+      </c>
+      <c r="K336" s="7" t="n">
+        <v>26</v>
       </c>
       <c r="L336" s="7" t="n">
         <v>47.5</v>
       </c>
       <c r="M336" s="9" t="n">
-        <v>33.47</v>
+        <v>33.27</v>
       </c>
       <c r="N336" s="9" t="n">
-        <v>70.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="O336" s="9" t="n">
         <v>335</v>
       </c>
       <c r="P336" s="10" t="n">
-        <v>4.97</v>
+        <v>6.68</v>
       </c>
       <c r="Q336" s="10" t="n">
-        <v>14.33</v>
+        <v>13.38</v>
       </c>
       <c r="R336" s="10" t="n">
-        <v>7.94</v>
+        <v>6.23</v>
       </c>
       <c r="S336" s="10" t="n">
-        <v>9.539999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="T336" s="10" t="n">
-        <v>2.62</v>
+        <v>3.23</v>
       </c>
       <c r="U336" s="10" t="n">
-        <v>4.44</v>
+        <v>4.92</v>
       </c>
       <c r="V336" s="10" t="n">
-        <v>1.16</v>
+        <v>0.82</v>
       </c>
       <c r="W336" s="10" t="n">
-        <v>2.47</v>
+        <v>1.3</v>
       </c>
       <c r="X336" s="9" t="b">
         <v>0</v>
@@ -33099,10 +33099,10 @@
         <v>0</v>
       </c>
       <c r="AA336" s="9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB336" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC336" s="9" t="n"/>
       <c r="AD336" s="9" t="b">
@@ -33112,12 +33112,12 @@
     <row r="337">
       <c r="A337" s="5" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B337" s="5" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C337" s="5" t="inlineStr">
@@ -33126,64 +33126,64 @@
         </is>
       </c>
       <c r="D337" s="11" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E337" s="8" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="F337" s="7" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="G337" s="6" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="H337" s="7" t="n">
-        <v>32.3</v>
+        <v>22.6</v>
+      </c>
+      <c r="E337" s="6" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="F337" s="8" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="G337" s="8" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="H337" s="11" t="n">
+        <v>26.2</v>
       </c>
       <c r="I337" s="7" t="n">
-        <v>49.2</v>
+        <v>44.4</v>
       </c>
       <c r="J337" s="11" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="K337" s="7" t="n">
-        <v>26</v>
+        <v>23.3</v>
+      </c>
+      <c r="K337" s="8" t="n">
+        <v>49.3</v>
       </c>
       <c r="L337" s="7" t="n">
         <v>47.5</v>
       </c>
       <c r="M337" s="9" t="n">
-        <v>33.27</v>
+        <v>33.47</v>
       </c>
       <c r="N337" s="9" t="n">
-        <v>68.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="O337" s="9" t="n">
         <v>335</v>
       </c>
       <c r="P337" s="10" t="n">
-        <v>6.68</v>
+        <v>4.97</v>
       </c>
       <c r="Q337" s="10" t="n">
-        <v>13.38</v>
+        <v>14.33</v>
       </c>
       <c r="R337" s="10" t="n">
-        <v>6.23</v>
+        <v>7.94</v>
       </c>
       <c r="S337" s="10" t="n">
-        <v>10.9</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="T337" s="10" t="n">
-        <v>3.23</v>
+        <v>2.62</v>
       </c>
       <c r="U337" s="10" t="n">
-        <v>4.92</v>
+        <v>4.44</v>
       </c>
       <c r="V337" s="10" t="n">
-        <v>0.82</v>
+        <v>1.16</v>
       </c>
       <c r="W337" s="10" t="n">
-        <v>1.3</v>
+        <v>2.47</v>
       </c>
       <c r="X337" s="9" t="b">
         <v>0</v>
@@ -33195,10 +33195,10 @@
         <v>0</v>
       </c>
       <c r="AA337" s="9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB337" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC337" s="9" t="n"/>
       <c r="AD337" s="9" t="b">
@@ -35512,42 +35512,42 @@
     <row r="362">
       <c r="A362" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="B362" s="5" t="inlineStr">
         <is>
-          <t>Home Depot, Inc. (The)</t>
+          <t>CBRE Group Inc</t>
         </is>
       </c>
       <c r="C362" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="D362" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="E362" s="7" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="F362" s="7" t="n">
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D362" s="7" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E362" s="8" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F362" s="6" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="G362" s="11" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="H362" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I362" s="8" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="J362" s="7" t="n">
         <v>36.7</v>
       </c>
-      <c r="G362" s="7" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="H362" s="6" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="I362" s="7" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="J362" s="11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K362" s="7" t="n">
-        <v>34</v>
+      <c r="K362" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="L362" s="7" t="n">
         <v>45.9</v>
@@ -35556,46 +35556,46 @@
         <v>28.29</v>
       </c>
       <c r="N362" s="9" t="n">
-        <v>71.09999999999999</v>
+        <v>56.5</v>
       </c>
       <c r="O362" s="9" t="n">
         <v>361</v>
       </c>
       <c r="P362" s="10" t="n">
-        <v>11.44</v>
+        <v>7.64</v>
       </c>
       <c r="Q362" s="10" t="n">
-        <v>10.58</v>
+        <v>13.76</v>
       </c>
       <c r="R362" s="10" t="n">
-        <v>4.77</v>
+        <v>10.98</v>
       </c>
       <c r="S362" s="10" t="n">
-        <v>5.09</v>
+        <v>3.81</v>
       </c>
       <c r="T362" s="10" t="n">
-        <v>6.96</v>
+        <v>1.14</v>
       </c>
       <c r="U362" s="10" t="n">
-        <v>5.04</v>
+        <v>6.18</v>
       </c>
       <c r="V362" s="10" t="n">
-        <v>0.33</v>
+        <v>1.83</v>
       </c>
       <c r="W362" s="10" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="X362" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y362" s="9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Z362" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA362" s="9" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="AB362" s="9" t="b">
         <v>0</v>
@@ -35608,90 +35608,90 @@
     <row r="363">
       <c r="A363" s="5" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B363" s="5" t="inlineStr">
         <is>
-          <t>CBRE Group Inc</t>
+          <t>Uber Technologies, Inc.</t>
         </is>
       </c>
       <c r="C363" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="D363" s="7" t="n">
-        <v>34.7</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D363" s="6" t="n">
+        <v>73.7</v>
       </c>
       <c r="E363" s="8" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="F363" s="6" t="n">
-        <v>84.5</v>
+        <v>57.7</v>
+      </c>
+      <c r="F363" s="8" t="n">
+        <v>51.6</v>
       </c>
       <c r="G363" s="11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H363" s="11" t="n">
         <v>29.3</v>
       </c>
-      <c r="H363" s="11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="I363" s="8" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="J363" s="7" t="n">
-        <v>36.7</v>
+      <c r="I363" s="7" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J363" s="11" t="n">
+        <v>11</v>
       </c>
       <c r="K363" s="11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L363" s="7" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="M363" s="9" t="n">
         <v>28.09</v>
       </c>
       <c r="N363" s="9" t="n">
-        <v>56.5</v>
+        <v>60</v>
       </c>
       <c r="O363" s="9" t="n">
         <v>362</v>
       </c>
       <c r="P363" s="10" t="n">
-        <v>7.64</v>
+        <v>16.22</v>
       </c>
       <c r="Q363" s="10" t="n">
-        <v>13.76</v>
+        <v>12.69</v>
       </c>
       <c r="R363" s="10" t="n">
-        <v>10.98</v>
+        <v>6.7</v>
       </c>
       <c r="S363" s="10" t="n">
-        <v>3.81</v>
+        <v>1.89</v>
       </c>
       <c r="T363" s="10" t="n">
-        <v>1.14</v>
+        <v>2.93</v>
       </c>
       <c r="U363" s="10" t="n">
-        <v>6.18</v>
+        <v>4.07</v>
       </c>
       <c r="V363" s="10" t="n">
-        <v>1.83</v>
+        <v>0.55</v>
       </c>
       <c r="W363" s="10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X363" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y363" s="9" t="n">
-        <v>4.6</v>
+        <v>20.1</v>
       </c>
       <c r="Z363" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA363" s="9" t="n">
-        <v>19.9</v>
+        <v>3.2</v>
       </c>
       <c r="AB363" s="9" t="b">
         <v>0</v>
@@ -35704,42 +35704,42 @@
     <row r="364">
       <c r="A364" s="5" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B364" s="5" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc.</t>
+          <t>Home Depot, Inc. (The)</t>
         </is>
       </c>
       <c r="C364" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D364" s="6" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="E364" s="8" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="F364" s="8" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="G364" s="11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H364" s="11" t="n">
-        <v>29.3</v>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D364" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="E364" s="7" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="F364" s="11" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="G364" s="7" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H364" s="6" t="n">
+        <v>69.59999999999999</v>
       </c>
       <c r="I364" s="7" t="n">
-        <v>40.7</v>
+        <v>50.4</v>
       </c>
       <c r="J364" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K364" s="11" t="n">
-        <v>16</v>
+        <v>6.5</v>
+      </c>
+      <c r="K364" s="7" t="n">
+        <v>34</v>
       </c>
       <c r="L364" s="7" t="n">
         <v>45.8</v>
@@ -35748,46 +35748,46 @@
         <v>27.89</v>
       </c>
       <c r="N364" s="9" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="O364" s="9" t="n">
         <v>363</v>
       </c>
       <c r="P364" s="10" t="n">
-        <v>16.22</v>
+        <v>11.44</v>
       </c>
       <c r="Q364" s="10" t="n">
-        <v>12.69</v>
+        <v>10.58</v>
       </c>
       <c r="R364" s="10" t="n">
-        <v>6.7</v>
+        <v>4.63</v>
       </c>
       <c r="S364" s="10" t="n">
-        <v>1.89</v>
+        <v>5.09</v>
       </c>
       <c r="T364" s="10" t="n">
-        <v>2.93</v>
+        <v>6.96</v>
       </c>
       <c r="U364" s="10" t="n">
-        <v>4.07</v>
+        <v>5.04</v>
       </c>
       <c r="V364" s="10" t="n">
-        <v>0.55</v>
+        <v>0.33</v>
       </c>
       <c r="W364" s="10" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="X364" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y364" s="9" t="n">
-        <v>20.1</v>
+        <v>0</v>
       </c>
       <c r="Z364" s="9" t="b">
         <v>0</v>
       </c>
       <c r="AA364" s="9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB364" s="9" t="b">
         <v>0</v>
@@ -38870,90 +38870,90 @@
     <row r="397">
       <c r="A397" s="5" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B397" s="5" t="inlineStr">
         <is>
-          <t>Republic Services, Inc.</t>
+          <t>ON Semiconductor Corporation</t>
         </is>
       </c>
       <c r="C397" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D397" s="7" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="E397" s="7" t="n">
-        <v>39.7</v>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D397" s="8" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="E397" s="11" t="n">
+        <v>31.4</v>
       </c>
       <c r="F397" s="11" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="G397" s="11" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H397" s="6" t="n">
-        <v>93.09999999999999</v>
+        <v>6.4</v>
+      </c>
+      <c r="G397" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="H397" s="11" t="n">
+        <v>24.9</v>
       </c>
       <c r="I397" s="7" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="J397" s="7" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="K397" s="7" t="n">
-        <v>46.9</v>
+        <v>44.1</v>
+      </c>
+      <c r="J397" s="8" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="K397" s="6" t="n">
+        <v>78.09999999999999</v>
       </c>
       <c r="L397" s="11" t="n">
         <v>43.9</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>21.12</v>
+        <v>21.31</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>70.59999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="O397" s="9" t="n">
         <v>396</v>
       </c>
       <c r="P397" s="10" t="n">
-        <v>9.19</v>
+        <v>13.69</v>
       </c>
       <c r="Q397" s="10" t="n">
-        <v>8.74</v>
+        <v>6.9</v>
       </c>
       <c r="R397" s="10" t="n">
-        <v>4.05</v>
+        <v>0.83</v>
       </c>
       <c r="S397" s="10" t="n">
-        <v>3.72</v>
+        <v>7.93</v>
       </c>
       <c r="T397" s="10" t="n">
-        <v>9.31</v>
+        <v>2.49</v>
       </c>
       <c r="U397" s="10" t="n">
-        <v>4.72</v>
+        <v>4.41</v>
       </c>
       <c r="V397" s="10" t="n">
-        <v>1.83</v>
+        <v>3.77</v>
       </c>
       <c r="W397" s="10" t="n">
-        <v>2.35</v>
+        <v>3.9</v>
       </c>
       <c r="X397" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y397" s="9" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="Z397" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA397" s="9" t="n">
-        <v>1.1</v>
+        <v>8.6</v>
       </c>
       <c r="AB397" s="9" t="b">
         <v>0</v>
@@ -38966,90 +38966,90 @@
     <row r="398">
       <c r="A398" s="5" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B398" s="5" t="inlineStr">
         <is>
-          <t>ON Semiconductor Corporation</t>
+          <t>Republic Services, Inc.</t>
         </is>
       </c>
       <c r="C398" s="5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="D398" s="8" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="E398" s="11" t="n">
-        <v>31.4</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D398" s="7" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="E398" s="7" t="n">
+        <v>39.7</v>
       </c>
       <c r="F398" s="11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G398" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="H398" s="11" t="n">
-        <v>24.9</v>
+        <v>31.2</v>
+      </c>
+      <c r="G398" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H398" s="6" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="I398" s="7" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="J398" s="8" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="K398" s="6" t="n">
-        <v>78.09999999999999</v>
+        <v>47.2</v>
+      </c>
+      <c r="J398" s="7" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="K398" s="7" t="n">
+        <v>46.9</v>
       </c>
       <c r="L398" s="11" t="n">
         <v>43.9</v>
       </c>
       <c r="M398" s="9" t="n">
-        <v>21.31</v>
+        <v>21.12</v>
       </c>
       <c r="N398" s="9" t="n">
-        <v>61.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O398" s="9" t="n">
         <v>396</v>
       </c>
       <c r="P398" s="10" t="n">
-        <v>13.69</v>
+        <v>9.19</v>
       </c>
       <c r="Q398" s="10" t="n">
-        <v>6.9</v>
+        <v>8.74</v>
       </c>
       <c r="R398" s="10" t="n">
-        <v>0.83</v>
+        <v>4.05</v>
       </c>
       <c r="S398" s="10" t="n">
-        <v>7.93</v>
+        <v>3.72</v>
       </c>
       <c r="T398" s="10" t="n">
-        <v>2.49</v>
+        <v>9.31</v>
       </c>
       <c r="U398" s="10" t="n">
-        <v>4.41</v>
+        <v>4.72</v>
       </c>
       <c r="V398" s="10" t="n">
-        <v>3.77</v>
+        <v>1.83</v>
       </c>
       <c r="W398" s="10" t="n">
-        <v>3.9</v>
+        <v>2.35</v>
       </c>
       <c r="X398" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y398" s="9" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="Z398" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA398" s="9" t="n">
-        <v>8.6</v>
+        <v>1.1</v>
       </c>
       <c r="AB398" s="9" t="b">
         <v>0</v>
@@ -49207,7 +49207,7 @@
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-07</t>
+          <t>Generated: 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -49482,30 +49482,30 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>CF Industries Holdings, Inc.</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E12" s="22" t="n">
         <v>68.40000000000001</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>93</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>84.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>79.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I12" s="21" t="b">
         <v>0</v>
@@ -49517,30 +49517,30 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>CF Industries Holdings, Inc.</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E13" s="22" t="n">
         <v>68.40000000000001</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>88.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>74.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>77.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I13" s="21" t="b">
         <v>0</v>
@@ -49954,7 +49954,7 @@
         <v>65.5</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>88.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G25" s="21" t="n">
         <v>66.7</v>
@@ -50021,7 +50021,7 @@
         </is>
       </c>
       <c r="E27" s="22" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F27" s="21" t="n">
         <v>77.40000000000001</v>
@@ -50505,7 +50505,7 @@
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-07</t>
+          <t>Generated: 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -50688,7 +50688,7 @@
         <v>2.88</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
@@ -50822,17 +50822,17 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>CF Industries Holdings, Inc.</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="E13" s="22" t="n">
@@ -50845,7 +50845,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>3.13</v>
+        <v>3.51</v>
       </c>
       <c r="I13" s="21" t="n">
         <v>4.06</v>
@@ -50862,17 +50862,17 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>CF Industries Holdings, Inc.</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E14" s="22" t="n">
@@ -50885,7 +50885,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>3.51</v>
+        <v>3.13</v>
       </c>
       <c r="I14" s="21" t="n">
         <v>4.06</v>
@@ -51396,7 +51396,7 @@
         </is>
       </c>
       <c r="E27" s="22" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F27" s="21" t="n">
         <v>4</v>
@@ -51408,7 +51408,7 @@
         <v>4.46</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="J27" s="21" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
       </c>
       <c r="B54" s="27" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -52905,7 +52905,7 @@
         <v>-0.301</v>
       </c>
       <c r="S2" s="9" t="n">
-        <v>0.301</v>
+        <v>0.3</v>
       </c>
       <c r="T2" s="9" t="n">
         <v>-0.298</v>
@@ -52962,7 +52962,7 @@
         <v>0.188</v>
       </c>
       <c r="AL2" s="9" t="n">
-        <v>-0.138</v>
+        <v>-0.137</v>
       </c>
       <c r="AM2" s="9" t="n">
         <v>0.013</v>
@@ -52974,7 +52974,7 @@
         <v>0.346</v>
       </c>
       <c r="AP2" s="9" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="AQ2" s="9" t="n">
         <v>-0.25</v>
@@ -53150,10 +53150,10 @@
         <v>0.356</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>0.135</v>
+        <v>0.136</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>-0.106</v>
+        <v>-0.105</v>
       </c>
       <c r="J4" s="9" t="n">
         <v>0.111</v>
@@ -53168,7 +53168,7 @@
         <v>-0.016</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>-0.048</v>
+        <v>-0.047</v>
       </c>
       <c r="O4" s="9" t="n">
         <v>0.19</v>
@@ -53183,10 +53183,10 @@
         <v>-0.463</v>
       </c>
       <c r="S4" s="9" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="T4" s="9" t="n">
-        <v>-0.173</v>
+        <v>-0.174</v>
       </c>
       <c r="U4" s="9" t="n">
         <v>-0.101</v>
@@ -53219,16 +53219,16 @@
         <v>0.005</v>
       </c>
       <c r="AE4" s="9" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
       <c r="AF4" s="9" t="n">
-        <v>-0.034</v>
+        <v>-0.035</v>
       </c>
       <c r="AG4" s="9" t="n">
         <v>0.053</v>
       </c>
       <c r="AH4" s="9" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="AI4" s="9" t="n">
         <v>-0.013</v>
@@ -53240,19 +53240,19 @@
         <v>0.025</v>
       </c>
       <c r="AL4" s="9" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="AM4" s="9" t="n">
-        <v>0.273</v>
+        <v>0.272</v>
       </c>
       <c r="AN4" s="9" t="n">
         <v>-0.095</v>
       </c>
       <c r="AO4" s="9" t="n">
-        <v>0.225</v>
+        <v>0.226</v>
       </c>
       <c r="AP4" s="9" t="n">
-        <v>-0.055</v>
+        <v>-0.054</v>
       </c>
       <c r="AQ4" s="9" t="n">
         <v>-0.055</v>
@@ -53261,7 +53261,7 @@
         <v>-0.273</v>
       </c>
       <c r="AS4" s="9" t="n">
-        <v>0.27</v>
+        <v>0.271</v>
       </c>
     </row>
     <row r="5">
@@ -53383,7 +53383,7 @@
         <v>0.253</v>
       </c>
       <c r="AP5" s="9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AQ5" s="9" t="n">
         <v>-0.268</v>
@@ -53631,7 +53631,7 @@
         <v>-0.229</v>
       </c>
       <c r="AP7" s="9" t="n">
-        <v>-0.068</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="AQ7" s="9" t="n">
         <v>0.143</v>
@@ -53656,7 +53656,7 @@
         <v>0.133</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.135</v>
+        <v>0.136</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>-0.1</v>
@@ -53750,7 +53750,7 @@
         <v>-0.064</v>
       </c>
       <c r="AL8" s="9" t="n">
-        <v>-0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="AM8" s="9" t="n">
         <v>0.305</v>
@@ -53762,7 +53762,7 @@
         <v>-0.1</v>
       </c>
       <c r="AP8" s="9" t="n">
-        <v>-0.019</v>
+        <v>-0.018</v>
       </c>
       <c r="AQ8" s="9" t="n">
         <v>-0.046</v>
@@ -53787,7 +53787,7 @@
         <v>-0.065</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>-0.106</v>
+        <v>-0.105</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>-0.195</v>
@@ -53824,7 +53824,7 @@
         <v>-0.056</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>-0.174</v>
+        <v>-0.173</v>
       </c>
       <c r="T9" s="9" t="n">
         <v>0.166</v>
@@ -53893,7 +53893,7 @@
         <v>-0.234</v>
       </c>
       <c r="AP9" s="9" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="AQ9" s="9" t="n">
         <v>-0.017</v>
@@ -53952,7 +53952,7 @@
       <c r="P10" s="9" t="n"/>
       <c r="Q10" s="9" t="n"/>
       <c r="R10" s="9" t="n">
-        <v>-0.193</v>
+        <v>-0.192</v>
       </c>
       <c r="S10" s="9" t="n">
         <v>-0.239</v>
@@ -54012,7 +54012,7 @@
         <v>-0.14</v>
       </c>
       <c r="AL10" s="9" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AM10" s="9" t="n">
         <v>0.318</v>
@@ -54024,7 +54024,7 @@
         <v>-0.305</v>
       </c>
       <c r="AP10" s="9" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="AQ10" s="9" t="n">
         <v>0.08500000000000001</v>
@@ -54094,7 +54094,7 @@
         <v>-0.034</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>-0.092</v>
+        <v>-0.093</v>
       </c>
       <c r="T11" s="9" t="n">
         <v>0.196</v>
@@ -54151,7 +54151,7 @@
         <v>0.167</v>
       </c>
       <c r="AL11" s="9" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="AM11" s="9" t="n">
         <v>0.283</v>
@@ -54163,7 +54163,7 @@
         <v>-0.193</v>
       </c>
       <c r="AP11" s="9" t="n">
-        <v>-0.04</v>
+        <v>-0.041</v>
       </c>
       <c r="AQ11" s="9" t="n">
         <v>0.089</v>
@@ -54230,10 +54230,10 @@
         <v>0.146</v>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
       <c r="T12" s="9" t="n">
         <v>-0.104</v>
@@ -54302,7 +54302,7 @@
         <v>0.065</v>
       </c>
       <c r="AP12" s="9" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="AQ12" s="9" t="n">
         <v>-0.178</v>
@@ -54361,10 +54361,10 @@
       <c r="P13" s="9" t="n"/>
       <c r="Q13" s="9" t="n"/>
       <c r="R13" s="9" t="n">
-        <v>0.067</v>
+        <v>0.066</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="T13" s="9" t="n">
         <v>0.099</v>
@@ -54458,7 +54458,7 @@
         <v>0.128</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>-0.048</v>
+        <v>-0.047</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>0.053</v>
@@ -54495,7 +54495,7 @@
         <v>0.068</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>0.073</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="T14" s="9" t="n">
         <v>-0.195</v>
@@ -54958,16 +54958,16 @@
         <v>-0.056</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>-0.193</v>
+        <v>-0.192</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>-0.034</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>0.067</v>
+        <v>0.066</v>
       </c>
       <c r="N18" s="9" t="n">
         <v>0.068</v>
@@ -54991,13 +54991,13 @@
         <v>0.156</v>
       </c>
       <c r="U18" s="9" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>-0.247</v>
+        <v>-0.248</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>0.125</v>
+        <v>0.124</v>
       </c>
       <c r="X18" s="9" t="n">
         <v>0.137</v>
@@ -55042,7 +55042,7 @@
         <v>-0.026</v>
       </c>
       <c r="AL18" s="9" t="n">
-        <v>0.102</v>
+        <v>0.103</v>
       </c>
       <c r="AM18" s="9" t="n">
         <v>-0.173</v>
@@ -55051,16 +55051,16 @@
         <v>0.106</v>
       </c>
       <c r="AO18" s="9" t="n">
-        <v>-0.103</v>
+        <v>-0.104</v>
       </c>
       <c r="AP18" s="9" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="AQ18" s="9" t="n">
         <v>0.059</v>
       </c>
       <c r="AR18" s="9" t="n">
-        <v>0.251</v>
+        <v>0.25</v>
       </c>
       <c r="AS18" s="9" t="n">
         <v>-0.262</v>
@@ -55073,13 +55073,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>0.301</v>
+        <v>0.3</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0.241</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>0.282</v>
@@ -55094,22 +55094,22 @@
         <v>-0.166</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-0.174</v>
+        <v>-0.173</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>-0.239</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>-0.092</v>
+        <v>-0.093</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>0.073</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O19" s="9" t="n">
         <v>-0.539</v>
@@ -55127,13 +55127,13 @@
         <v>1</v>
       </c>
       <c r="T19" s="9" t="n">
-        <v>-0.036</v>
+        <v>-0.037</v>
       </c>
       <c r="U19" s="9" t="n">
-        <v>-0.092</v>
+        <v>-0.091</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>-0.178</v>
+        <v>-0.179</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0.054</v>
@@ -55157,49 +55157,49 @@
         <v>0.038</v>
       </c>
       <c r="AD19" s="9" t="n">
-        <v>-0.129</v>
+        <v>-0.128</v>
       </c>
       <c r="AE19" s="9" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AF19" s="9" t="n">
-        <v>0.127</v>
+        <v>0.126</v>
       </c>
       <c r="AG19" s="9" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="AH19" s="9" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="AI19" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ19" s="9" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="AK19" s="9" t="n">
         <v>0.105</v>
       </c>
       <c r="AL19" s="9" t="n">
-        <v>-0.017</v>
+        <v>-0.016</v>
       </c>
       <c r="AM19" s="9" t="n">
         <v>-0.191</v>
       </c>
       <c r="AN19" s="9" t="n">
-        <v>-0.068</v>
+        <v>-0.067</v>
       </c>
       <c r="AO19" s="9" t="n">
-        <v>0.119</v>
+        <v>0.118</v>
       </c>
       <c r="AP19" s="9" t="n">
-        <v>0.047</v>
+        <v>0.05</v>
       </c>
       <c r="AQ19" s="9" t="n">
-        <v>-0.101</v>
+        <v>-0.1</v>
       </c>
       <c r="AR19" s="9" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="AS19" s="9" t="n">
         <v>-0.254</v>
@@ -55218,7 +55218,7 @@
         <v>-0.225</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>-0.173</v>
+        <v>-0.174</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>-0.278</v>
@@ -55263,7 +55263,7 @@
         <v>0.156</v>
       </c>
       <c r="S20" s="9" t="n">
-        <v>-0.036</v>
+        <v>-0.037</v>
       </c>
       <c r="T20" s="33" t="n">
         <v>1</v>
@@ -55320,7 +55320,7 @@
         <v>-0.418</v>
       </c>
       <c r="AL20" s="9" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="AM20" s="9" t="n">
         <v>0.182</v>
@@ -55332,7 +55332,7 @@
         <v>-0.283</v>
       </c>
       <c r="AP20" s="9" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="AQ20" s="9" t="n">
         <v>0.172</v>
@@ -55399,10 +55399,10 @@
         <v>0.23</v>
       </c>
       <c r="R21" s="9" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="S21" s="9" t="n">
-        <v>-0.092</v>
+        <v>-0.091</v>
       </c>
       <c r="T21" s="9" t="n">
         <v>0.5580000000000001</v>
@@ -55538,10 +55538,10 @@
         <v>0.133</v>
       </c>
       <c r="R22" s="9" t="n">
-        <v>-0.247</v>
+        <v>-0.248</v>
       </c>
       <c r="S22" s="9" t="n">
-        <v>-0.178</v>
+        <v>-0.179</v>
       </c>
       <c r="T22" s="9" t="n">
         <v>0.169</v>
@@ -55598,7 +55598,7 @@
         <v>-0.241</v>
       </c>
       <c r="AL22" s="9" t="n">
-        <v>-0.078</v>
+        <v>-0.079</v>
       </c>
       <c r="AM22" s="9" t="n">
         <v>0.37</v>
@@ -55677,7 +55677,7 @@
         <v>-0.419</v>
       </c>
       <c r="R23" s="9" t="n">
-        <v>0.125</v>
+        <v>0.124</v>
       </c>
       <c r="S23" s="9" t="n">
         <v>0.054</v>
@@ -55737,7 +55737,7 @@
         <v>-0.123</v>
       </c>
       <c r="AL23" s="9" t="n">
-        <v>0.493</v>
+        <v>0.492</v>
       </c>
       <c r="AM23" s="9" t="n">
         <v>-0.092</v>
@@ -56015,7 +56015,7 @@
         <v>-0.089</v>
       </c>
       <c r="AL25" s="9" t="n">
-        <v>0.591</v>
+        <v>0.59</v>
       </c>
       <c r="AM25" s="9" t="n">
         <v>-0.039</v>
@@ -56027,7 +56027,7 @@
         <v>-0.189</v>
       </c>
       <c r="AP25" s="9" t="n">
-        <v>-0.104</v>
+        <v>-0.105</v>
       </c>
       <c r="AQ25" s="9" t="n">
         <v>0.218</v>
@@ -56305,7 +56305,7 @@
         <v>0.25</v>
       </c>
       <c r="AP27" s="9" t="n">
-        <v>-0.157</v>
+        <v>-0.158</v>
       </c>
       <c r="AQ27" s="9" t="n">
         <v>0.068</v>
@@ -56432,7 +56432,7 @@
         <v>-0.128</v>
       </c>
       <c r="AL28" s="9" t="n">
-        <v>0.581</v>
+        <v>0.58</v>
       </c>
       <c r="AM28" s="9" t="n">
         <v>-0.08599999999999999</v>
@@ -56571,7 +56571,7 @@
         <v>-0.124</v>
       </c>
       <c r="AL29" s="9" t="n">
-        <v>0.582</v>
+        <v>0.581</v>
       </c>
       <c r="AM29" s="9" t="n">
         <v>-0.091</v>
@@ -56583,7 +56583,7 @@
         <v>-0.202</v>
       </c>
       <c r="AP29" s="9" t="n">
-        <v>-0.048</v>
+        <v>-0.049</v>
       </c>
       <c r="AQ29" s="9" t="n">
         <v>0.172</v>
@@ -56653,7 +56653,7 @@
         <v>-0.045</v>
       </c>
       <c r="S30" s="9" t="n">
-        <v>-0.129</v>
+        <v>-0.128</v>
       </c>
       <c r="T30" s="9" t="n">
         <v>-0.047</v>
@@ -56747,7 +56747,7 @@
         <v>0.076</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>0.115</v>
@@ -56792,7 +56792,7 @@
         <v>-0.109</v>
       </c>
       <c r="S31" s="9" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="T31" s="9" t="n">
         <v>0.008</v>
@@ -56861,7 +56861,7 @@
         <v>-0.078</v>
       </c>
       <c r="AP31" s="9" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AQ31" s="9" t="n">
         <v>0.045</v>
@@ -56886,7 +56886,7 @@
         <v>-0.122</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>-0.034</v>
+        <v>-0.035</v>
       </c>
       <c r="E32" s="9" t="n">
         <v>-0.015</v>
@@ -56931,7 +56931,7 @@
         <v>0.118</v>
       </c>
       <c r="S32" s="9" t="n">
-        <v>0.127</v>
+        <v>0.126</v>
       </c>
       <c r="T32" s="9" t="n">
         <v>0.231</v>
@@ -57070,7 +57070,7 @@
         <v>-0.064</v>
       </c>
       <c r="S33" s="9" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="T33" s="9" t="n">
         <v>-0.031</v>
@@ -57164,7 +57164,7 @@
         <v>-0.013</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>-0.034</v>
@@ -57209,7 +57209,7 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="T34" s="9" t="n">
         <v>0.062</v>
@@ -57278,7 +57278,7 @@
         <v>-0.138</v>
       </c>
       <c r="AP34" s="9" t="n">
-        <v>-0.049</v>
+        <v>-0.05</v>
       </c>
       <c r="AQ34" s="9" t="n">
         <v>0.158</v>
@@ -57487,7 +57487,7 @@
         <v>-0.132</v>
       </c>
       <c r="S36" s="9" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="T36" s="9" t="n">
         <v>-0.253</v>
@@ -57544,7 +57544,7 @@
         <v>0.284</v>
       </c>
       <c r="AL36" s="9" t="n">
-        <v>-0.248</v>
+        <v>-0.247</v>
       </c>
       <c r="AM36" s="9" t="n">
         <v>-0.225</v>
@@ -57556,7 +57556,7 @@
         <v>0.174</v>
       </c>
       <c r="AP36" s="9" t="n">
-        <v>0.273</v>
+        <v>0.274</v>
       </c>
       <c r="AQ36" s="29" t="n">
         <v>-0.664</v>
@@ -57714,13 +57714,13 @@
         </is>
       </c>
       <c r="B38" s="9" t="n">
-        <v>-0.138</v>
+        <v>-0.137</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>-0.033</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="E38" s="9" t="n">
         <v>-0.182</v>
@@ -57732,16 +57732,16 @@
         <v>0.011</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>-0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="I38" s="9" t="n">
         <v>-0.024</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>-0.01</v>
@@ -57762,28 +57762,28 @@
         <v>-0.388</v>
       </c>
       <c r="R38" s="9" t="n">
-        <v>0.102</v>
+        <v>0.103</v>
       </c>
       <c r="S38" s="9" t="n">
-        <v>-0.017</v>
+        <v>-0.016</v>
       </c>
       <c r="T38" s="9" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="U38" s="9" t="n">
         <v>-0.108</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>-0.078</v>
+        <v>-0.079</v>
       </c>
       <c r="W38" s="9" t="n">
-        <v>0.493</v>
+        <v>0.492</v>
       </c>
       <c r="X38" s="9" t="n">
         <v>0.544</v>
       </c>
       <c r="Y38" s="9" t="n">
-        <v>0.591</v>
+        <v>0.59</v>
       </c>
       <c r="Z38" s="9" t="n">
         <v>0.39</v>
@@ -57792,10 +57792,10 @@
         <v>0.134</v>
       </c>
       <c r="AB38" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AC38" s="9" t="n">
         <v>0.581</v>
-      </c>
-      <c r="AC38" s="9" t="n">
-        <v>0.582</v>
       </c>
       <c r="AD38" s="29" t="n">
         <v>0.635</v>
@@ -57816,7 +57816,7 @@
         <v>-0.137</v>
       </c>
       <c r="AJ38" s="9" t="n">
-        <v>-0.248</v>
+        <v>-0.247</v>
       </c>
       <c r="AK38" s="9" t="n">
         <v>-0.027</v>
@@ -57825,13 +57825,13 @@
         <v>1</v>
       </c>
       <c r="AM38" s="9" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="AN38" s="9" t="n">
         <v>-0.102</v>
       </c>
       <c r="AO38" s="9" t="n">
-        <v>-0.038</v>
+        <v>-0.037</v>
       </c>
       <c r="AP38" s="9" t="n">
         <v>-0.179</v>
@@ -57843,7 +57843,7 @@
         <v>-0.019</v>
       </c>
       <c r="AS38" s="9" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="39">
@@ -57859,7 +57859,7 @@
         <v>-0.012</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.273</v>
+        <v>0.272</v>
       </c>
       <c r="E39" s="29" t="n">
         <v>-0.656</v>
@@ -57953,7 +57953,7 @@
         <v>-0.111</v>
       </c>
       <c r="AL39" s="9" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="AM39" s="33" t="n">
         <v>1</v>
@@ -57965,7 +57965,7 @@
         <v>-0.1</v>
       </c>
       <c r="AP39" s="9" t="n">
-        <v>-0.073</v>
+        <v>-0.074</v>
       </c>
       <c r="AQ39" s="9" t="n">
         <v>0.181</v>
@@ -58027,7 +58027,7 @@
         <v>0.106</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>-0.068</v>
+        <v>-0.067</v>
       </c>
       <c r="T40" s="9" t="n">
         <v>0.04</v>
@@ -58096,7 +58096,7 @@
         <v>-0.217</v>
       </c>
       <c r="AP40" s="9" t="n">
-        <v>0.101</v>
+        <v>0.102</v>
       </c>
       <c r="AQ40" s="9" t="n">
         <v>-0.041</v>
@@ -58121,7 +58121,7 @@
         <v>0.268</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.225</v>
+        <v>0.226</v>
       </c>
       <c r="E41" s="9" t="n">
         <v>0.253</v>
@@ -58163,10 +58163,10 @@
         <v>-0.049</v>
       </c>
       <c r="R41" s="9" t="n">
-        <v>-0.103</v>
+        <v>-0.104</v>
       </c>
       <c r="S41" s="9" t="n">
-        <v>0.119</v>
+        <v>0.118</v>
       </c>
       <c r="T41" s="9" t="n">
         <v>-0.283</v>
@@ -58223,7 +58223,7 @@
         <v>0.25</v>
       </c>
       <c r="AL41" s="9" t="n">
-        <v>-0.038</v>
+        <v>-0.037</v>
       </c>
       <c r="AM41" s="9" t="n">
         <v>-0.1</v>
@@ -58254,37 +58254,37 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>-0.039</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>-0.055</v>
+        <v>-0.054</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>-0.248</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>-0.068</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>-0.019</v>
+        <v>-0.018</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>-0.04</v>
+        <v>-0.041</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="M42" s="9" t="n">
         <v>0.012</v>
@@ -58302,13 +58302,13 @@
         <v>0.151</v>
       </c>
       <c r="R42" s="9" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>0.047</v>
+        <v>0.05</v>
       </c>
       <c r="T42" s="9" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="U42" s="9" t="n">
         <v>0.077</v>
@@ -58323,25 +58323,25 @@
         <v>-0.005</v>
       </c>
       <c r="Y42" s="9" t="n">
-        <v>-0.104</v>
+        <v>-0.105</v>
       </c>
       <c r="Z42" s="9" t="n">
         <v>-0.203</v>
       </c>
       <c r="AA42" s="9" t="n">
-        <v>-0.157</v>
+        <v>-0.158</v>
       </c>
       <c r="AB42" s="9" t="n">
         <v>-0.052</v>
       </c>
       <c r="AC42" s="9" t="n">
-        <v>-0.048</v>
+        <v>-0.049</v>
       </c>
       <c r="AD42" s="9" t="n">
         <v>-0.143</v>
       </c>
       <c r="AE42" s="9" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AF42" s="9" t="n">
         <v>0.091</v>
@@ -58350,13 +58350,13 @@
         <v>0.031</v>
       </c>
       <c r="AH42" s="9" t="n">
-        <v>-0.049</v>
+        <v>-0.05</v>
       </c>
       <c r="AI42" s="9" t="n">
         <v>-0.067</v>
       </c>
       <c r="AJ42" s="9" t="n">
-        <v>0.273</v>
+        <v>0.274</v>
       </c>
       <c r="AK42" s="9" t="n">
         <v>-0.045</v>
@@ -58365,10 +58365,10 @@
         <v>-0.179</v>
       </c>
       <c r="AM42" s="9" t="n">
-        <v>-0.073</v>
+        <v>-0.074</v>
       </c>
       <c r="AN42" s="9" t="n">
-        <v>0.101</v>
+        <v>0.102</v>
       </c>
       <c r="AO42" s="9" t="n">
         <v>-0.139</v>
@@ -58377,13 +58377,13 @@
         <v>1</v>
       </c>
       <c r="AQ42" s="9" t="n">
-        <v>-0.237</v>
+        <v>-0.238</v>
       </c>
       <c r="AR42" s="9" t="n">
         <v>-0.076</v>
       </c>
       <c r="AS42" s="9" t="n">
-        <v>-0.059</v>
+        <v>-0.061</v>
       </c>
     </row>
     <row r="43">
@@ -58444,7 +58444,7 @@
         <v>0.059</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>-0.101</v>
+        <v>-0.1</v>
       </c>
       <c r="T43" s="9" t="n">
         <v>0.172</v>
@@ -58513,7 +58513,7 @@
         <v>-0.118</v>
       </c>
       <c r="AP43" s="9" t="n">
-        <v>-0.237</v>
+        <v>-0.238</v>
       </c>
       <c r="AQ43" s="33" t="n">
         <v>1</v>
@@ -58580,10 +58580,10 @@
         <v>-0.244</v>
       </c>
       <c r="R44" s="9" t="n">
-        <v>0.251</v>
+        <v>0.25</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="T44" s="9" t="n">
         <v>0.409</v>
@@ -58677,7 +58677,7 @@
         <v>0.092</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.27</v>
+        <v>0.271</v>
       </c>
       <c r="E45" s="9" t="n">
         <v>-0.231</v>
@@ -58771,7 +58771,7 @@
         <v>-0.253</v>
       </c>
       <c r="AL45" s="9" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="AM45" s="9" t="n">
         <v>0.463</v>
@@ -58783,7 +58783,7 @@
         <v>-0.248</v>
       </c>
       <c r="AP45" s="9" t="n">
-        <v>-0.059</v>
+        <v>-0.061</v>
       </c>
       <c r="AQ45" s="9" t="n">
         <v>0.162</v>
@@ -59066,13 +59066,13 @@
         <v>0.09412385643912738</v>
       </c>
       <c r="P4" s="35" t="n">
-        <v>0.546223736913199</v>
+        <v>0.5462235554526463</v>
       </c>
       <c r="Q4" s="35" t="n">
-        <v>0.2469195919230219</v>
+        <v>0.2469195873565474</v>
       </c>
       <c r="R4" s="9" t="n">
-        <v>0.6998311409081371</v>
+        <v>0.6998310248724425</v>
       </c>
       <c r="S4" s="35" t="n">
         <v>0.6019626015873615</v>
@@ -59150,7 +59150,7 @@
         <v>4.702233250620347</v>
       </c>
       <c r="N5" s="35" t="n">
-        <v>0.5323513513513513</v>
+        <v>0.5313888190954773</v>
       </c>
       <c r="O5" s="35" t="n">
         <v>0.1467387334745453</v>
@@ -59159,10 +59159,10 @@
         <v>0.4851727884810282</v>
       </c>
       <c r="Q5" s="35" t="n">
-        <v>0.4824737813683501</v>
+        <v>0.4824736899799266</v>
       </c>
       <c r="R5" s="9" t="n">
-        <v>1.044856533635584</v>
+        <v>1.044856635478588</v>
       </c>
       <c r="S5" s="35" t="n">
         <v>0.1093060482515122</v>
@@ -59249,10 +59249,10 @@
         <v>0.5302405251440804</v>
       </c>
       <c r="Q6" s="35" t="n">
-        <v>0.4590065315484569</v>
+        <v>0.4590065002004002</v>
       </c>
       <c r="R6" s="9" t="n">
-        <v>-0.7387348571111659</v>
+        <v>-0.7387354178835264</v>
       </c>
       <c r="S6" s="35" t="n">
         <v>0.192464970042622</v>
@@ -59337,10 +59337,10 @@
         <v>0.618575081555008</v>
       </c>
       <c r="Q7" s="35" t="n">
-        <v>0.2948226379525046</v>
+        <v>0.2948225926857158</v>
       </c>
       <c r="R7" s="9" t="n">
-        <v>-0.04657318538262101</v>
+        <v>-0.04657331589117929</v>
       </c>
       <c r="S7" s="35" t="n">
         <v>0.1243314121176603</v>
@@ -59427,10 +59427,10 @@
         <v>0.9872662102515311</v>
       </c>
       <c r="Q8" s="35" t="n">
-        <v>0.3499072283540974</v>
+        <v>0.3499072572750672</v>
       </c>
       <c r="R8" s="9" t="n">
-        <v>-0.274929571628772</v>
+        <v>-0.2749291691967286</v>
       </c>
       <c r="S8" s="35" t="n">
         <v>0.2186210720761638</v>
@@ -59558,7 +59558,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
@@ -59583,59 +59583,55 @@
       </c>
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="n">
-        <v>5.132179324825428</v>
+        <v>6.597934556949521</v>
       </c>
       <c r="J10" s="35" t="n">
-        <v>0.08933120456622443</v>
+        <v>-0.005824147442073251</v>
       </c>
       <c r="K10" s="35" t="n">
-        <v>0.1040090261797904</v>
+        <v>0.1804458493618319</v>
       </c>
       <c r="L10" s="35" t="n">
-        <v>0.3238112783835214</v>
+        <v>0.08736255705528066</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>0.6285664578983995</v>
+        <v>2.483883849620629</v>
       </c>
       <c r="N10" s="35" t="n">
-        <v>-0.2310059347181009</v>
+        <v>-0.328610939112487</v>
       </c>
       <c r="O10" s="35" t="n">
-        <v>0.3037398921832884</v>
+        <v>0.1036422524007046</v>
       </c>
       <c r="P10" s="35" t="n">
-        <v>0.4078731935228759</v>
+        <v>0.3185494605555942</v>
       </c>
       <c r="Q10" s="35" t="n">
-        <v>0.4225582976370982</v>
+        <v>0.3760712970413534</v>
       </c>
       <c r="R10" s="9" t="n">
-        <v>-0.9411005475350573</v>
+        <v>0.06396034085381784</v>
       </c>
       <c r="S10" s="35" t="n">
-        <v>0.07997560646249237</v>
+        <v>0.1720333522701407</v>
       </c>
       <c r="T10" s="9" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="U10" s="9" t="n">
-        <v>133.35</v>
+        <v>56.77</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>125.03789</v>
+        <v>68.21429000000001</v>
       </c>
       <c r="W10" s="9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X10" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y10" s="9" t="n"/>
-      <c r="Z10" s="29" t="inlineStr">
-        <is>
-          <t>API EV=24.5B vs computed=21.3B (ratio=1.15)</t>
-        </is>
-      </c>
+      <c r="Z10" s="9" t="n"/>
       <c r="AA10" s="9" t="b">
         <v>0</v>
       </c>
@@ -59652,7 +59648,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
@@ -59677,55 +59673,59 @@
       </c>
       <c r="H11" s="9" t="n"/>
       <c r="I11" s="9" t="n">
-        <v>6.597934556949521</v>
+        <v>5.132179324825428</v>
       </c>
       <c r="J11" s="35" t="n">
-        <v>-0.005824147442073251</v>
+        <v>0.08933120456622443</v>
       </c>
       <c r="K11" s="35" t="n">
-        <v>0.1804458493618319</v>
+        <v>0.1040090261797904</v>
       </c>
       <c r="L11" s="35" t="n">
-        <v>0.08736255705528066</v>
+        <v>0.3238112783835214</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>2.483883849620629</v>
+        <v>0.6285664578983995</v>
       </c>
       <c r="N11" s="35" t="n">
-        <v>-0.328610939112487</v>
+        <v>-0.2310059347181009</v>
       </c>
       <c r="O11" s="35" t="n">
-        <v>0.1036422524007046</v>
+        <v>0.3037398921832884</v>
       </c>
       <c r="P11" s="35" t="n">
-        <v>0.3185495576300814</v>
+        <v>0.4078730632838979</v>
       </c>
       <c r="Q11" s="35" t="n">
-        <v>0.3760713199765136</v>
+        <v>0.4225582852849112</v>
       </c>
       <c r="R11" s="9" t="n">
-        <v>0.063961025052965</v>
+        <v>-0.9411003868146838</v>
       </c>
       <c r="S11" s="35" t="n">
-        <v>0.1720333522701407</v>
+        <v>0.07997560646249237</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="U11" s="9" t="n">
-        <v>56.77</v>
+        <v>133.35</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>68.21429000000001</v>
+        <v>125.03789</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X11" s="9" t="b">
         <v>0</v>
       </c>
       <c r="Y11" s="9" t="n"/>
-      <c r="Z11" s="9" t="n"/>
+      <c r="Z11" s="29" t="inlineStr">
+        <is>
+          <t>API EV=24.5B vs computed=21.3B (ratio=1.15)</t>
+        </is>
+      </c>
       <c r="AA11" s="9" t="b">
         <v>0</v>
       </c>
@@ -59782,13 +59782,13 @@
         <v>0.09182082972526175</v>
       </c>
       <c r="P12" s="35" t="n">
-        <v>0.2892566290321509</v>
+        <v>0.2892567252884464</v>
       </c>
       <c r="Q12" s="35" t="n">
-        <v>0.2453599025512486</v>
+        <v>0.2453599527645732</v>
       </c>
       <c r="R12" s="9" t="n">
-        <v>-0.3635213116113742</v>
+        <v>-0.363521520144823</v>
       </c>
       <c r="S12" s="35" t="n">
         <v>0.4751920077909821</v>
@@ -59872,13 +59872,13 @@
         <v>0.1417119545837077</v>
       </c>
       <c r="P13" s="35" t="n">
-        <v>0.5234374707931873</v>
+        <v>0.5234373591200898</v>
       </c>
       <c r="Q13" s="35" t="n">
-        <v>0.4420456629291085</v>
+        <v>0.442045730705584</v>
       </c>
       <c r="R13" s="9" t="n">
-        <v>1.164472502490347</v>
+        <v>1.164472606002391</v>
       </c>
       <c r="S13" s="35" t="n">
         <v>0.1479060123400983</v>
